--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_oil_gas_distribution.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07484350764588704</v>
+        <v>0.07472982063059527</v>
       </c>
       <c r="C2">
-        <v>7075.926645133146</v>
+        <v>7026.7327602259</v>
       </c>
       <c r="D2">
-        <v>6513.926645133146</v>
+        <v>6539.524760225901</v>
       </c>
       <c r="E2">
-        <v>-2336.8</v>
+        <v>-2262.008</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>74.792</v>
       </c>
       <c r="G2">
         <v>562</v>
@@ -1451,28 +1451,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.7620376</v>
       </c>
       <c r="N2">
-        <v>673.4428571428572</v>
+        <v>669.6808195428572</v>
       </c>
       <c r="O2">
-        <v>134.6885714285714</v>
+        <v>133.9361639085714</v>
       </c>
       <c r="P2">
-        <v>538.7542857142857</v>
+        <v>535.7446556342858</v>
       </c>
       <c r="Q2">
-        <v>857.4542857142857</v>
+        <v>854.4446556342857</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07484350764588704</v>
+        <v>0.07507820265716694</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5706866652781318</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>179.0101345990952</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07472982063059527</v>
+        <v>0.07461613361530348</v>
       </c>
       <c r="C3">
-        <v>7026.7327602259</v>
+        <v>6977.74085753743</v>
       </c>
       <c r="D3">
-        <v>6539.524760225901</v>
+        <v>6565.32485753743</v>
       </c>
       <c r="E3">
-        <v>-2262.008</v>
+        <v>-2187.216</v>
       </c>
       <c r="F3">
-        <v>74.792</v>
+        <v>149.584</v>
       </c>
       <c r="G3">
         <v>562</v>
@@ -1533,28 +1533,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M3">
-        <v>3.7620376</v>
+        <v>7.5240752</v>
       </c>
       <c r="N3">
-        <v>669.6808195428572</v>
+        <v>665.9187819428572</v>
       </c>
       <c r="O3">
-        <v>133.9361639085714</v>
+        <v>133.1837563885715</v>
       </c>
       <c r="P3">
-        <v>535.7446556342858</v>
+        <v>532.7350255542858</v>
       </c>
       <c r="Q3">
-        <v>854.4446556342857</v>
+        <v>851.4350255542857</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07507820265716694</v>
+        <v>0.07531768736255458</v>
       </c>
       <c r="T3">
-        <v>0.5706866652781318</v>
+        <v>0.5753546679387848</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>179.0101345990952</v>
+        <v>89.50506729954762</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07461613361530348</v>
+        <v>0.07450244660001172</v>
       </c>
       <c r="C4">
-        <v>6977.74085753743</v>
+        <v>6928.953337151161</v>
       </c>
       <c r="D4">
-        <v>6565.32485753743</v>
+        <v>6591.329337151161</v>
       </c>
       <c r="E4">
-        <v>-2187.216</v>
+        <v>-2112.424</v>
       </c>
       <c r="F4">
-        <v>149.584</v>
+        <v>224.376</v>
       </c>
       <c r="G4">
         <v>562</v>
@@ -1615,28 +1615,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M4">
-        <v>7.5240752</v>
+        <v>11.2861128</v>
       </c>
       <c r="N4">
-        <v>665.9187819428572</v>
+        <v>662.1567443428572</v>
       </c>
       <c r="O4">
-        <v>133.1837563885715</v>
+        <v>132.4313488685715</v>
       </c>
       <c r="P4">
-        <v>532.7350255542858</v>
+        <v>529.7253954742857</v>
       </c>
       <c r="Q4">
-        <v>851.4350255542857</v>
+        <v>848.4253954742857</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07531768736255458</v>
+        <v>0.07556210989691929</v>
       </c>
       <c r="T4">
-        <v>0.5753546679387848</v>
+        <v>0.5801189180769769</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>89.50506729954762</v>
+        <v>59.67004486636509</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07450244660001172</v>
+        <v>0.07438875958471994</v>
       </c>
       <c r="C5">
-        <v>6928.953337151161</v>
+        <v>6880.372637327556</v>
       </c>
       <c r="D5">
-        <v>6591.329337151161</v>
+        <v>6617.540637327555</v>
       </c>
       <c r="E5">
-        <v>-2112.424</v>
+        <v>-2037.632</v>
       </c>
       <c r="F5">
-        <v>224.376</v>
+        <v>299.168</v>
       </c>
       <c r="G5">
         <v>562</v>
@@ -1697,28 +1697,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M5">
-        <v>11.2861128</v>
+        <v>15.0481504</v>
       </c>
       <c r="N5">
-        <v>662.1567443428572</v>
+        <v>658.3947067428571</v>
       </c>
       <c r="O5">
-        <v>132.4313488685715</v>
+        <v>131.6789413485714</v>
       </c>
       <c r="P5">
-        <v>529.7253954742857</v>
+        <v>526.7157653942857</v>
       </c>
       <c r="Q5">
-        <v>848.4253954742857</v>
+        <v>845.4157653942856</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07556210989691929</v>
+        <v>0.07581162456741661</v>
       </c>
       <c r="T5">
-        <v>0.5801189180769769</v>
+        <v>0.5849824234263816</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>59.67004486636509</v>
+        <v>44.75253364977381</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07438875958471994</v>
+        <v>0.07427507256942815</v>
       </c>
       <c r="C6">
-        <v>6880.372637327556</v>
+        <v>6832.001235266174</v>
       </c>
       <c r="D6">
-        <v>6617.540637327555</v>
+        <v>6643.961235266174</v>
       </c>
       <c r="E6">
-        <v>-2037.632</v>
+        <v>-1962.84</v>
       </c>
       <c r="F6">
-        <v>299.168</v>
+        <v>373.96</v>
       </c>
       <c r="G6">
         <v>562</v>
@@ -1779,28 +1779,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M6">
-        <v>15.0481504</v>
+        <v>18.810188</v>
       </c>
       <c r="N6">
-        <v>658.3947067428571</v>
+        <v>654.6326691428571</v>
       </c>
       <c r="O6">
-        <v>131.6789413485714</v>
+        <v>130.9265338285714</v>
       </c>
       <c r="P6">
-        <v>526.7157653942857</v>
+        <v>523.7061353142857</v>
       </c>
       <c r="Q6">
-        <v>845.4157653942856</v>
+        <v>842.4061353142856</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07581162456741661</v>
+        <v>0.07606639217834543</v>
       </c>
       <c r="T6">
-        <v>0.5849824234263816</v>
+        <v>0.5899483183620893</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>44.75253364977381</v>
+        <v>35.80202691981904</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07427507256942815</v>
+        <v>0.0741613855541364</v>
       </c>
       <c r="C7">
-        <v>6832.001235266174</v>
+        <v>6783.841647886134</v>
       </c>
       <c r="D7">
-        <v>6643.961235266174</v>
+        <v>6670.593647886134</v>
       </c>
       <c r="E7">
-        <v>-1962.84</v>
+        <v>-1888.048</v>
       </c>
       <c r="F7">
-        <v>373.96</v>
+        <v>448.752</v>
       </c>
       <c r="G7">
         <v>562</v>
@@ -1861,28 +1861,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M7">
-        <v>18.810188</v>
+        <v>22.5722256</v>
       </c>
       <c r="N7">
-        <v>654.6326691428571</v>
+        <v>650.8706315428572</v>
       </c>
       <c r="O7">
-        <v>130.9265338285714</v>
+        <v>130.1741263085714</v>
       </c>
       <c r="P7">
-        <v>523.7061353142857</v>
+        <v>520.6965052342857</v>
       </c>
       <c r="Q7">
-        <v>842.4061353142856</v>
+        <v>839.3965052342857</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07606639217834543</v>
+        <v>0.07632658037674085</v>
       </c>
       <c r="T7">
-        <v>0.5899483183620893</v>
+        <v>0.5950198706368549</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.80202691981904</v>
+        <v>29.83502243318254</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0741613855541364</v>
+        <v>0.07404769853884462</v>
       </c>
       <c r="C8">
-        <v>6783.841647886135</v>
+        <v>6735.896432625417</v>
       </c>
       <c r="D8">
-        <v>6670.593647886134</v>
+        <v>6697.440432625417</v>
       </c>
       <c r="E8">
-        <v>-1888.048</v>
+        <v>-1813.256</v>
       </c>
       <c r="F8">
-        <v>448.752</v>
+        <v>523.544</v>
       </c>
       <c r="G8">
         <v>562</v>
@@ -1943,28 +1943,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M8">
-        <v>22.5722256</v>
+        <v>26.3342632</v>
       </c>
       <c r="N8">
-        <v>650.8706315428572</v>
+        <v>647.1085939428572</v>
       </c>
       <c r="O8">
-        <v>130.1741263085714</v>
+        <v>129.4217187885714</v>
       </c>
       <c r="P8">
-        <v>520.6965052342857</v>
+        <v>517.6868751542858</v>
       </c>
       <c r="Q8">
-        <v>839.3965052342857</v>
+        <v>836.3868751542857</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07632658037674085</v>
+        <v>0.07659236402026304</v>
       </c>
       <c r="T8">
-        <v>0.5950198706368549</v>
+        <v>0.6002004885519379</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.83502243318254</v>
+        <v>25.57287637129932</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07404769853884462</v>
+        <v>0.07393401152355286</v>
       </c>
       <c r="C9">
-        <v>6735.896432625417</v>
+        <v>6688.168188259485</v>
       </c>
       <c r="D9">
-        <v>6697.440432625417</v>
+        <v>6724.504188259485</v>
       </c>
       <c r="E9">
-        <v>-1813.256</v>
+        <v>-1738.464</v>
       </c>
       <c r="F9">
-        <v>523.544</v>
+        <v>598.336</v>
       </c>
       <c r="G9">
         <v>562</v>
@@ -2025,28 +2025,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M9">
-        <v>26.3342632</v>
+        <v>30.0963008</v>
       </c>
       <c r="N9">
-        <v>647.1085939428572</v>
+        <v>643.3465563428572</v>
       </c>
       <c r="O9">
-        <v>129.4217187885714</v>
+        <v>128.6693112685714</v>
       </c>
       <c r="P9">
-        <v>517.6868751542858</v>
+        <v>514.6772450742858</v>
       </c>
       <c r="Q9">
-        <v>836.3868751542857</v>
+        <v>833.3772450742857</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07659236402026304</v>
+        <v>0.07686392556907919</v>
       </c>
       <c r="T9">
-        <v>0.6002004885519379</v>
+        <v>0.6054937285956096</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.57287637129932</v>
+        <v>22.3762668248869</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07393401152355286</v>
+        <v>0.07382032450826106</v>
       </c>
       <c r="C10">
-        <v>6688.168188259485</v>
+        <v>6640.659555739939</v>
       </c>
       <c r="D10">
-        <v>6724.504188259485</v>
+        <v>6751.787555739938</v>
       </c>
       <c r="E10">
-        <v>-1738.464</v>
+        <v>-1663.672</v>
       </c>
       <c r="F10">
-        <v>598.336</v>
+        <v>673.1279999999999</v>
       </c>
       <c r="G10">
         <v>562</v>
@@ -2107,28 +2107,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M10">
-        <v>30.0963008</v>
+        <v>33.85833839999999</v>
       </c>
       <c r="N10">
-        <v>643.3465563428572</v>
+        <v>639.5845187428572</v>
       </c>
       <c r="O10">
-        <v>128.6693112685714</v>
+        <v>127.9169037485714</v>
       </c>
       <c r="P10">
-        <v>514.6772450742858</v>
+        <v>511.6676149942858</v>
       </c>
       <c r="Q10">
-        <v>833.3772450742857</v>
+        <v>830.3676149942858</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07686392556907919</v>
+        <v>0.07714145550358359</v>
       </c>
       <c r="T10">
-        <v>0.6054937285956096</v>
+        <v>0.610903303585296</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.3762668248869</v>
+        <v>19.89001495545503</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07382032450826106</v>
+        <v>0.0737066374929693</v>
       </c>
       <c r="C11">
-        <v>6640.659555739939</v>
+        <v>6593.373219053534</v>
       </c>
       <c r="D11">
-        <v>6751.787555739938</v>
+        <v>6779.293219053534</v>
       </c>
       <c r="E11">
-        <v>-1663.672</v>
+        <v>-1588.88</v>
       </c>
       <c r="F11">
-        <v>673.1279999999999</v>
+        <v>747.92</v>
       </c>
       <c r="G11">
         <v>562</v>
@@ -2189,28 +2189,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M11">
-        <v>33.85833839999999</v>
+        <v>37.62037599999999</v>
       </c>
       <c r="N11">
-        <v>639.5845187428572</v>
+        <v>635.8224811428572</v>
       </c>
       <c r="O11">
-        <v>127.9169037485714</v>
+        <v>127.1644962285715</v>
       </c>
       <c r="P11">
-        <v>511.6676149942858</v>
+        <v>508.6579849142857</v>
       </c>
       <c r="Q11">
-        <v>830.3676149942858</v>
+        <v>827.3579849142857</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07714145550358359</v>
+        <v>0.07742515276996588</v>
       </c>
       <c r="T11">
-        <v>0.610903303585296</v>
+        <v>0.616433091352531</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.89001495545503</v>
+        <v>17.90101345990953</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07370663749296931</v>
+        <v>0.07359295047767753</v>
       </c>
       <c r="C12">
-        <v>6593.37321905353</v>
+        <v>6546.311906102428</v>
       </c>
       <c r="D12">
-        <v>6779.29321905353</v>
+        <v>6807.023906102429</v>
       </c>
       <c r="E12">
-        <v>-1588.88</v>
+        <v>-1514.088</v>
       </c>
       <c r="F12">
-        <v>747.9200000000001</v>
+        <v>822.712</v>
       </c>
       <c r="G12">
         <v>562</v>
@@ -2271,28 +2271,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M12">
-        <v>37.620376</v>
+        <v>41.3824136</v>
       </c>
       <c r="N12">
-        <v>635.8224811428572</v>
+        <v>632.0604435428572</v>
       </c>
       <c r="O12">
-        <v>127.1644962285715</v>
+        <v>126.4120887085714</v>
       </c>
       <c r="P12">
-        <v>508.6579849142857</v>
+        <v>505.6483548342858</v>
       </c>
       <c r="Q12">
-        <v>827.3579849142857</v>
+        <v>824.3483548342857</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07742515276996589</v>
+        <v>0.07771522525581745</v>
       </c>
       <c r="T12">
-        <v>0.6164330913525312</v>
+        <v>0.6220871440134119</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.90101345990952</v>
+        <v>16.27364859991775</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07359295047767753</v>
+        <v>0.07347926346238574</v>
       </c>
       <c r="C13">
-        <v>6546.311906102428</v>
+        <v>6499.478389606018</v>
       </c>
       <c r="D13">
-        <v>6807.023906102429</v>
+        <v>6834.982389606018</v>
       </c>
       <c r="E13">
-        <v>-1514.088</v>
+        <v>-1439.296</v>
       </c>
       <c r="F13">
-        <v>822.712</v>
+        <v>897.5039999999999</v>
       </c>
       <c r="G13">
         <v>562</v>
@@ -2353,28 +2353,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M13">
-        <v>41.3824136</v>
+        <v>45.14445119999999</v>
       </c>
       <c r="N13">
-        <v>632.0604435428572</v>
+        <v>628.2984059428572</v>
       </c>
       <c r="O13">
-        <v>126.4120887085714</v>
+        <v>125.6596811885715</v>
       </c>
       <c r="P13">
-        <v>505.6483548342858</v>
+        <v>502.6387247542858</v>
       </c>
       <c r="Q13">
-        <v>824.3483548342857</v>
+        <v>821.3387247542857</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07771522525581745</v>
+        <v>0.07801189029816563</v>
       </c>
       <c r="T13">
-        <v>0.6220871440134119</v>
+        <v>0.627869697871131</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.27364859991775</v>
+        <v>14.91751121659127</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07347926346238574</v>
+        <v>0.07336557644709399</v>
       </c>
       <c r="C14">
-        <v>6499.478389606018</v>
+        <v>6452.875488025105</v>
       </c>
       <c r="D14">
-        <v>6834.982389606018</v>
+        <v>6863.171488025106</v>
       </c>
       <c r="E14">
-        <v>-1439.296</v>
+        <v>-1364.504</v>
       </c>
       <c r="F14">
-        <v>897.5039999999999</v>
+        <v>972.296</v>
       </c>
       <c r="G14">
         <v>562</v>
@@ -2435,28 +2435,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M14">
-        <v>45.14445119999999</v>
+        <v>48.9064888</v>
       </c>
       <c r="N14">
-        <v>628.2984059428572</v>
+        <v>624.5363683428571</v>
       </c>
       <c r="O14">
-        <v>125.6596811885715</v>
+        <v>124.9072736685714</v>
       </c>
       <c r="P14">
-        <v>502.6387247542858</v>
+        <v>499.6290946742857</v>
       </c>
       <c r="Q14">
-        <v>821.3387247542857</v>
+        <v>818.3290946742857</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07801189029816563</v>
+        <v>0.0783153752265448</v>
       </c>
       <c r="T14">
-        <v>0.627869697871131</v>
+        <v>0.6337851840014411</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.91751121659127</v>
+        <v>13.77001035377656</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07336557644709399</v>
+        <v>0.07325188943180219</v>
       </c>
       <c r="C15">
-        <v>6452.875488025105</v>
+        <v>6406.5060665091</v>
       </c>
       <c r="D15">
-        <v>6863.171488025106</v>
+        <v>6891.594066509099</v>
       </c>
       <c r="E15">
-        <v>-1364.504</v>
+        <v>-1289.712</v>
       </c>
       <c r="F15">
-        <v>972.296</v>
+        <v>1047.088</v>
       </c>
       <c r="G15">
         <v>562</v>
@@ -2517,28 +2517,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M15">
-        <v>48.9064888</v>
+        <v>52.6685264</v>
       </c>
       <c r="N15">
-        <v>624.5363683428571</v>
+        <v>620.7743307428572</v>
       </c>
       <c r="O15">
-        <v>124.9072736685714</v>
+        <v>124.1548661485714</v>
       </c>
       <c r="P15">
-        <v>499.6290946742857</v>
+        <v>496.6194645942857</v>
       </c>
       <c r="Q15">
-        <v>818.3290946742857</v>
+        <v>815.3194645942856</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0783153752265448</v>
+        <v>0.07862591794395604</v>
       </c>
       <c r="T15">
-        <v>0.6337851840014411</v>
+        <v>0.6398382395766424</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.77001035377656</v>
+        <v>12.78643818564966</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07325188943180219</v>
+        <v>0.07313820241651042</v>
       </c>
       <c r="C16">
-        <v>6406.5060665091</v>
+        <v>6360.373037866731</v>
       </c>
       <c r="D16">
-        <v>6891.594066509099</v>
+        <v>6920.253037866731</v>
       </c>
       <c r="E16">
-        <v>-1289.712</v>
+        <v>-1214.92</v>
       </c>
       <c r="F16">
-        <v>1047.088</v>
+        <v>1121.88</v>
       </c>
       <c r="G16">
         <v>562</v>
@@ -2599,28 +2599,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M16">
-        <v>52.6685264</v>
+        <v>56.430564</v>
       </c>
       <c r="N16">
-        <v>620.7743307428572</v>
+        <v>617.0122931428572</v>
       </c>
       <c r="O16">
-        <v>124.1548661485714</v>
+        <v>123.4024586285714</v>
       </c>
       <c r="P16">
-        <v>496.6194645942857</v>
+        <v>493.6098345142858</v>
       </c>
       <c r="Q16">
-        <v>815.3194645942856</v>
+        <v>812.3098345142857</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07862591794395604</v>
+        <v>0.07894376754883579</v>
       </c>
       <c r="T16">
-        <v>0.6398382395766424</v>
+        <v>0.6460337199889071</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.78643818564966</v>
+        <v>11.93400897327301</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07313820241651042</v>
+        <v>0.07302451540121864</v>
       </c>
       <c r="C17">
-        <v>6360.373037866731</v>
+        <v>6314.479363561215</v>
       </c>
       <c r="D17">
-        <v>6920.253037866731</v>
+        <v>6949.151363561215</v>
       </c>
       <c r="E17">
-        <v>-1214.92</v>
+        <v>-1140.128</v>
       </c>
       <c r="F17">
-        <v>1121.88</v>
+        <v>1196.672</v>
       </c>
       <c r="G17">
         <v>562</v>
@@ -2681,28 +2681,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M17">
-        <v>56.43056399999999</v>
+        <v>60.1926016</v>
       </c>
       <c r="N17">
-        <v>617.0122931428572</v>
+        <v>613.2502555428572</v>
       </c>
       <c r="O17">
-        <v>123.4024586285714</v>
+        <v>122.6500511085714</v>
       </c>
       <c r="P17">
-        <v>493.6098345142858</v>
+        <v>490.6002044342857</v>
       </c>
       <c r="Q17">
-        <v>812.3098345142857</v>
+        <v>809.3002044342857</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07894376754883579</v>
+        <v>0.07926918500145078</v>
       </c>
       <c r="T17">
-        <v>0.6460337199889071</v>
+        <v>0.6523767118395591</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.93400897327302</v>
+        <v>11.18813341244345</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07302451540121864</v>
+        <v>0.07291082838592687</v>
       </c>
       <c r="C18">
-        <v>6314.479363561215</v>
+        <v>6268.828054730362</v>
       </c>
       <c r="D18">
-        <v>6949.151363561215</v>
+        <v>6978.292054730362</v>
       </c>
       <c r="E18">
-        <v>-1140.128</v>
+        <v>-1065.336</v>
       </c>
       <c r="F18">
-        <v>1196.672</v>
+        <v>1271.464</v>
       </c>
       <c r="G18">
         <v>562</v>
@@ -2763,28 +2763,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M18">
-        <v>60.1926016</v>
+        <v>63.9546392</v>
       </c>
       <c r="N18">
-        <v>613.2502555428572</v>
+        <v>609.4882179428572</v>
       </c>
       <c r="O18">
-        <v>122.6500511085714</v>
+        <v>121.8976435885714</v>
       </c>
       <c r="P18">
-        <v>490.6002044342857</v>
+        <v>487.5905743542858</v>
       </c>
       <c r="Q18">
-        <v>809.3002044342857</v>
+        <v>806.2905743542857</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07926918500145078</v>
+        <v>0.07960244383846612</v>
       </c>
       <c r="T18">
-        <v>0.6523767118395591</v>
+        <v>0.6588725468673353</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.18813341244345</v>
+        <v>10.53000791759384</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07291082838592687</v>
+        <v>0.07279714137063512</v>
       </c>
       <c r="C19">
-        <v>6268.828054730362</v>
+        <v>6223.4221732325</v>
       </c>
       <c r="D19">
-        <v>6978.292054730362</v>
+        <v>7007.6781732325</v>
       </c>
       <c r="E19">
-        <v>-1065.336</v>
+        <v>-990.5440000000001</v>
       </c>
       <c r="F19">
-        <v>1271.464</v>
+        <v>1346.256</v>
       </c>
       <c r="G19">
         <v>562</v>
@@ -2845,28 +2845,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M19">
-        <v>63.9546392</v>
+        <v>67.7166768</v>
       </c>
       <c r="N19">
-        <v>609.4882179428572</v>
+        <v>605.7261803428572</v>
       </c>
       <c r="O19">
-        <v>121.8976435885714</v>
+        <v>121.1452360685714</v>
       </c>
       <c r="P19">
-        <v>487.5905743542858</v>
+        <v>484.5809442742858</v>
       </c>
       <c r="Q19">
-        <v>806.2905743542857</v>
+        <v>803.2809442742857</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07960244383846612</v>
+        <v>0.07994383093979891</v>
       </c>
       <c r="T19">
-        <v>0.6588725468673353</v>
+        <v>0.665526816895789</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.53000791759384</v>
+        <v>9.945007477727513</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0727971413706351</v>
+        <v>0.07268345435534333</v>
       </c>
       <c r="C20">
-        <v>6223.422173232504</v>
+        <v>6178.264832718954</v>
       </c>
       <c r="D20">
-        <v>7007.678173232504</v>
+        <v>7037.312832718953</v>
       </c>
       <c r="E20">
-        <v>-990.5440000000003</v>
+        <v>-915.7520000000002</v>
       </c>
       <c r="F20">
-        <v>1346.256</v>
+        <v>1421.048</v>
       </c>
       <c r="G20">
         <v>562</v>
@@ -2927,28 +2927,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M20">
-        <v>67.71667679999999</v>
+        <v>71.4787144</v>
       </c>
       <c r="N20">
-        <v>605.7261803428572</v>
+        <v>601.9641427428571</v>
       </c>
       <c r="O20">
-        <v>121.1452360685714</v>
+        <v>120.3928285485714</v>
       </c>
       <c r="P20">
-        <v>484.5809442742858</v>
+        <v>481.5713141942857</v>
       </c>
       <c r="Q20">
-        <v>803.2809442742857</v>
+        <v>800.2713141942857</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0799438309397989</v>
+        <v>0.08029364735227572</v>
       </c>
       <c r="T20">
-        <v>0.6655268168957889</v>
+        <v>0.6723453898879082</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.945007477727515</v>
+        <v>9.421586031531326</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07268345435534333</v>
+        <v>0.07256976734005155</v>
       </c>
       <c r="C21">
-        <v>6178.264832718954</v>
+        <v>6133.359199733782</v>
       </c>
       <c r="D21">
-        <v>7037.312832718953</v>
+        <v>7067.199199733782</v>
       </c>
       <c r="E21">
-        <v>-915.7520000000002</v>
+        <v>-840.96</v>
       </c>
       <c r="F21">
-        <v>1421.048</v>
+        <v>1495.84</v>
       </c>
       <c r="G21">
         <v>562</v>
@@ -3009,28 +3009,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M21">
-        <v>71.4787144</v>
+        <v>75.240752</v>
       </c>
       <c r="N21">
-        <v>601.9641427428571</v>
+        <v>598.2021051428571</v>
       </c>
       <c r="O21">
-        <v>120.3928285485714</v>
+        <v>119.6404210285714</v>
       </c>
       <c r="P21">
-        <v>481.5713141942857</v>
+        <v>478.5616841142857</v>
       </c>
       <c r="Q21">
-        <v>800.2713141942857</v>
+        <v>797.2616841142856</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08029364735227572</v>
+        <v>0.08065220917506444</v>
       </c>
       <c r="T21">
-        <v>0.6723453898879082</v>
+        <v>0.6793344272048302</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.421586031531326</v>
+        <v>8.95050672995476</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07256976734005155</v>
+        <v>0.07270808032475978</v>
       </c>
       <c r="C22">
-        <v>6133.359199733782</v>
+        <v>6022.240363963809</v>
       </c>
       <c r="D22">
-        <v>7067.199199733782</v>
+        <v>7030.872363963808</v>
       </c>
       <c r="E22">
-        <v>-840.96</v>
+        <v>-766.1680000000001</v>
       </c>
       <c r="F22">
-        <v>1495.84</v>
+        <v>1570.632</v>
       </c>
       <c r="G22">
         <v>562</v>
@@ -3091,45 +3091,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M22">
-        <v>75.240752</v>
+        <v>81.3587376</v>
       </c>
       <c r="N22">
-        <v>598.2021051428571</v>
+        <v>592.0841195428571</v>
       </c>
       <c r="O22">
-        <v>119.6404210285714</v>
+        <v>118.4168239085714</v>
       </c>
       <c r="P22">
-        <v>478.5616841142857</v>
+        <v>473.6672956342857</v>
       </c>
       <c r="Q22">
-        <v>797.2616841142856</v>
+        <v>792.3672956342857</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08065220917506444</v>
+        <v>0.08101984851235415</v>
       </c>
       <c r="T22">
-        <v>0.6793344272048302</v>
+        <v>0.6865004021753452</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>8.95050672995476</v>
+        <v>8.277449687750035</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07270808032475978</v>
+        <v>0.07260639330946803</v>
       </c>
       <c r="C23">
-        <v>6022.240363963809</v>
+        <v>5974.119181530909</v>
       </c>
       <c r="D23">
-        <v>7030.872363963808</v>
+        <v>7057.543181530909</v>
       </c>
       <c r="E23">
-        <v>-766.1680000000003</v>
+        <v>-691.3760000000002</v>
       </c>
       <c r="F23">
-        <v>1570.632</v>
+        <v>1645.424</v>
       </c>
       <c r="G23">
         <v>562</v>
@@ -3173,28 +3173,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M23">
-        <v>81.35873759999998</v>
+        <v>85.2329632</v>
       </c>
       <c r="N23">
-        <v>592.0841195428573</v>
+        <v>588.2098939428572</v>
       </c>
       <c r="O23">
-        <v>118.4168239085715</v>
+        <v>117.6419787885714</v>
       </c>
       <c r="P23">
-        <v>473.6672956342858</v>
+        <v>470.5679151542857</v>
       </c>
       <c r="Q23">
-        <v>792.3672956342857</v>
+        <v>789.2679151542857</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08101984851235415</v>
+        <v>0.08139691449931796</v>
       </c>
       <c r="T23">
-        <v>0.6865004021753452</v>
+        <v>0.6938501200938223</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.277449687750039</v>
+        <v>7.90120197467049</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07260639330946803</v>
+        <v>0.07250470629417624</v>
       </c>
       <c r="C24">
-        <v>5974.119181530909</v>
+        <v>5926.201115043492</v>
       </c>
       <c r="D24">
-        <v>7057.543181530909</v>
+        <v>7084.417115043492</v>
       </c>
       <c r="E24">
-        <v>-691.3760000000002</v>
+        <v>-616.5840000000001</v>
       </c>
       <c r="F24">
-        <v>1645.424</v>
+        <v>1720.216</v>
       </c>
       <c r="G24">
         <v>562</v>
@@ -3255,28 +3255,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M24">
-        <v>85.2329632</v>
+        <v>89.1071888</v>
       </c>
       <c r="N24">
-        <v>588.2098939428572</v>
+        <v>584.3356683428572</v>
       </c>
       <c r="O24">
-        <v>117.6419787885714</v>
+        <v>116.8671336685714</v>
       </c>
       <c r="P24">
-        <v>470.5679151542857</v>
+        <v>467.4685346742857</v>
       </c>
       <c r="Q24">
-        <v>789.2679151542857</v>
+        <v>786.1685346742856</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08139691449931796</v>
+        <v>0.08178377440802109</v>
       </c>
       <c r="T24">
-        <v>0.6938501200938223</v>
+        <v>0.7013907397764156</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.90120197467049</v>
+        <v>7.557671454032642</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07250470629417624</v>
+        <v>0.07240301927888447</v>
       </c>
       <c r="C25">
-        <v>5926.201115043492</v>
+        <v>5878.488493664344</v>
       </c>
       <c r="D25">
-        <v>7084.417115043492</v>
+        <v>7111.496493664344</v>
       </c>
       <c r="E25">
-        <v>-616.5840000000001</v>
+        <v>-541.7920000000001</v>
       </c>
       <c r="F25">
-        <v>1720.216</v>
+        <v>1795.008</v>
       </c>
       <c r="G25">
         <v>562</v>
@@ -3337,28 +3337,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M25">
-        <v>89.1071888</v>
+        <v>92.98141440000001</v>
       </c>
       <c r="N25">
-        <v>584.3356683428572</v>
+        <v>580.4614427428571</v>
       </c>
       <c r="O25">
-        <v>116.8671336685714</v>
+        <v>116.0922885485714</v>
       </c>
       <c r="P25">
-        <v>467.4685346742857</v>
+        <v>464.3691541942857</v>
       </c>
       <c r="Q25">
-        <v>786.1685346742856</v>
+        <v>783.0691541942856</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08178377440802109</v>
+        <v>0.08218081484063745</v>
       </c>
       <c r="T25">
-        <v>0.7013907397764156</v>
+        <v>0.7091297968190772</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.557671454032642</v>
+        <v>7.242768476781281</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07240301927888446</v>
+        <v>0.0723013322635927</v>
       </c>
       <c r="C26">
-        <v>5878.488493664348</v>
+        <v>5830.983682304745</v>
       </c>
       <c r="D26">
-        <v>7111.496493664348</v>
+        <v>7138.783682304746</v>
       </c>
       <c r="E26">
-        <v>-541.7920000000004</v>
+        <v>-467.0000000000002</v>
       </c>
       <c r="F26">
-        <v>1795.008</v>
+        <v>1869.8</v>
       </c>
       <c r="G26">
         <v>562</v>
@@ -3419,28 +3419,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M26">
-        <v>92.98141439999999</v>
+        <v>96.85563999999999</v>
       </c>
       <c r="N26">
-        <v>580.4614427428572</v>
+        <v>576.5872171428572</v>
       </c>
       <c r="O26">
-        <v>116.0922885485714</v>
+        <v>115.3174434285714</v>
       </c>
       <c r="P26">
-        <v>464.3691541942858</v>
+        <v>461.2697737142857</v>
       </c>
       <c r="Q26">
-        <v>783.0691541942857</v>
+        <v>779.9697737142857</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08218081484063744</v>
+        <v>0.08258844301812358</v>
       </c>
       <c r="T26">
-        <v>0.7091297968190771</v>
+        <v>0.7170752287162097</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.242768476781284</v>
+        <v>6.953057737710031</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0723013322635927</v>
+        <v>0.07255324524830091</v>
       </c>
       <c r="C27">
-        <v>5830.983682304745</v>
+        <v>5688.971713740002</v>
       </c>
       <c r="D27">
-        <v>7138.783682304746</v>
+        <v>7071.563713740003</v>
       </c>
       <c r="E27">
-        <v>-467.0000000000002</v>
+        <v>-392.2080000000001</v>
       </c>
       <c r="F27">
-        <v>1869.8</v>
+        <v>1944.592</v>
       </c>
       <c r="G27">
         <v>562</v>
@@ -3501,45 +3501,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M27">
-        <v>96.85563999999999</v>
+        <v>104.035672</v>
       </c>
       <c r="N27">
-        <v>576.5872171428572</v>
+        <v>569.4071851428572</v>
       </c>
       <c r="O27">
-        <v>115.3174434285714</v>
+        <v>113.8814370285714</v>
       </c>
       <c r="P27">
-        <v>461.2697737142857</v>
+        <v>455.5257481142858</v>
       </c>
       <c r="Q27">
-        <v>779.9697737142857</v>
+        <v>774.2257481142857</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08258844301812358</v>
+        <v>0.08300708817337961</v>
       </c>
       <c r="T27">
-        <v>0.7170752287162097</v>
+        <v>0.7252354020159674</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.953057737710031</v>
+        <v>6.473191783130474</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07255324524830091</v>
+        <v>0.07246515823300914</v>
       </c>
       <c r="C28">
-        <v>5688.971713740002</v>
+        <v>5637.540270446462</v>
       </c>
       <c r="D28">
-        <v>7071.563713740003</v>
+        <v>7094.924270446462</v>
       </c>
       <c r="E28">
-        <v>-392.2080000000001</v>
+        <v>-317.4160000000002</v>
       </c>
       <c r="F28">
-        <v>1944.592</v>
+        <v>2019.384</v>
       </c>
       <c r="G28">
         <v>562</v>
@@ -3583,28 +3583,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M28">
-        <v>104.035672</v>
+        <v>108.037044</v>
       </c>
       <c r="N28">
-        <v>569.4071851428572</v>
+        <v>565.4058131428571</v>
       </c>
       <c r="O28">
-        <v>113.8814370285714</v>
+        <v>113.0811626285714</v>
       </c>
       <c r="P28">
-        <v>455.5257481142858</v>
+        <v>452.3246505142857</v>
       </c>
       <c r="Q28">
-        <v>774.2257481142857</v>
+        <v>771.0246505142857</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08300708817337961</v>
+        <v>0.08343720305891664</v>
       </c>
       <c r="T28">
-        <v>0.7252354020159674</v>
+        <v>0.7336191417074993</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.473191783130474</v>
+        <v>6.233443939310828</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07246515823300914</v>
+        <v>0.07237707121771736</v>
       </c>
       <c r="C29">
-        <v>5637.540270446462</v>
+        <v>5586.26367955927</v>
       </c>
       <c r="D29">
-        <v>7094.924270446462</v>
+        <v>7118.439679559269</v>
       </c>
       <c r="E29">
-        <v>-317.4160000000002</v>
+        <v>-242.6240000000003</v>
       </c>
       <c r="F29">
-        <v>2019.384</v>
+        <v>2094.176</v>
       </c>
       <c r="G29">
         <v>562</v>
@@ -3665,28 +3665,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M29">
-        <v>108.037044</v>
+        <v>112.038416</v>
       </c>
       <c r="N29">
-        <v>565.4058131428571</v>
+        <v>561.4044411428572</v>
       </c>
       <c r="O29">
-        <v>113.0811626285714</v>
+        <v>112.2808882285714</v>
       </c>
       <c r="P29">
-        <v>452.3246505142857</v>
+        <v>449.1235529142858</v>
       </c>
       <c r="Q29">
-        <v>771.0246505142857</v>
+        <v>767.8235529142858</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08343720305891664</v>
+        <v>0.08387926558016301</v>
       </c>
       <c r="T29">
-        <v>0.7336191417074993</v>
+        <v>0.7422357630571292</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.233443939310828</v>
+        <v>6.010820941478298</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07237707121771736</v>
+        <v>0.07228898420242559</v>
       </c>
       <c r="C30">
-        <v>5586.26367955927</v>
+        <v>5535.143485926592</v>
       </c>
       <c r="D30">
-        <v>7118.439679559269</v>
+        <v>7142.111485926593</v>
       </c>
       <c r="E30">
-        <v>-242.6240000000003</v>
+        <v>-167.8319999999999</v>
       </c>
       <c r="F30">
-        <v>2094.176</v>
+        <v>2168.968</v>
       </c>
       <c r="G30">
         <v>562</v>
@@ -3747,28 +3747,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M30">
-        <v>112.038416</v>
+        <v>116.039788</v>
       </c>
       <c r="N30">
-        <v>561.4044411428572</v>
+        <v>557.4030691428571</v>
       </c>
       <c r="O30">
-        <v>112.2808882285714</v>
+        <v>111.4806138285714</v>
       </c>
       <c r="P30">
-        <v>449.1235529142858</v>
+        <v>445.9224553142857</v>
       </c>
       <c r="Q30">
-        <v>767.8235529142858</v>
+        <v>764.6224553142856</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08387926558016301</v>
+        <v>0.08433378056679661</v>
       </c>
       <c r="T30">
-        <v>0.7422357630571292</v>
+        <v>0.7510951061349179</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.010820941478298</v>
+        <v>5.803551253841114</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07228898420242559</v>
+        <v>0.07220089718713381</v>
       </c>
       <c r="C31">
-        <v>5535.143485926593</v>
+        <v>5484.181255014251</v>
       </c>
       <c r="D31">
-        <v>7142.111485926593</v>
+        <v>7165.941255014251</v>
       </c>
       <c r="E31">
-        <v>-167.8320000000003</v>
+        <v>-93.04000000000042</v>
       </c>
       <c r="F31">
-        <v>2168.968</v>
+        <v>2243.76</v>
       </c>
       <c r="G31">
         <v>562</v>
@@ -3829,28 +3829,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M31">
-        <v>116.039788</v>
+        <v>120.04116</v>
       </c>
       <c r="N31">
-        <v>557.4030691428572</v>
+        <v>553.4016971428572</v>
       </c>
       <c r="O31">
-        <v>111.4806138285714</v>
+        <v>110.6803394285714</v>
       </c>
       <c r="P31">
-        <v>445.9224553142858</v>
+        <v>442.7213577142858</v>
       </c>
       <c r="Q31">
-        <v>764.6224553142857</v>
+        <v>761.4213577142857</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08433378056679661</v>
+        <v>0.08480128169590545</v>
       </c>
       <c r="T31">
-        <v>0.7510951061349179</v>
+        <v>0.7602075733006434</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.803551253841116</v>
+        <v>5.610099545379745</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07220089718713381</v>
+        <v>0.07231121017184204</v>
       </c>
       <c r="C32">
-        <v>5484.181255014251</v>
+        <v>5379.571816920683</v>
       </c>
       <c r="D32">
-        <v>7165.941255014251</v>
+        <v>7136.123816920683</v>
       </c>
       <c r="E32">
-        <v>-93.04000000000042</v>
+        <v>-18.24800000000005</v>
       </c>
       <c r="F32">
-        <v>2243.76</v>
+        <v>2318.552</v>
       </c>
       <c r="G32">
         <v>562</v>
@@ -3911,45 +3911,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M32">
-        <v>120.04116</v>
+        <v>125.8973736</v>
       </c>
       <c r="N32">
-        <v>553.4016971428572</v>
+        <v>547.5454835428571</v>
       </c>
       <c r="O32">
-        <v>110.6803394285714</v>
+        <v>109.5090967085714</v>
       </c>
       <c r="P32">
-        <v>442.7213577142858</v>
+        <v>438.0363868342857</v>
       </c>
       <c r="Q32">
-        <v>761.4213577142857</v>
+        <v>756.7363868342857</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08480128169590545</v>
+        <v>0.08528233358237977</v>
       </c>
       <c r="T32">
-        <v>0.7602075733006434</v>
+        <v>0.7695841699494332</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>5.610099545379745</v>
+        <v>5.349141430722087</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07231121017184204</v>
+        <v>0.07222952315655026</v>
       </c>
       <c r="C33">
-        <v>5379.571816920683</v>
+        <v>5326.835782588469</v>
       </c>
       <c r="D33">
-        <v>7136.123816920683</v>
+        <v>7158.179782588469</v>
       </c>
       <c r="E33">
-        <v>-18.24800000000005</v>
+        <v>56.54399999999987</v>
       </c>
       <c r="F33">
-        <v>2318.552</v>
+        <v>2393.344</v>
       </c>
       <c r="G33">
         <v>562</v>
@@ -3993,28 +3993,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M33">
-        <v>125.8973736</v>
+        <v>129.9585792</v>
       </c>
       <c r="N33">
-        <v>547.5454835428571</v>
+        <v>543.4842779428571</v>
       </c>
       <c r="O33">
-        <v>109.5090967085714</v>
+        <v>108.6968555885714</v>
       </c>
       <c r="P33">
-        <v>438.0363868342857</v>
+        <v>434.7874223542857</v>
       </c>
       <c r="Q33">
-        <v>756.7363868342857</v>
+        <v>753.4874223542856</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08528233358237977</v>
+        <v>0.0857775340537504</v>
       </c>
       <c r="T33">
-        <v>0.7695841699494332</v>
+        <v>0.7792365488525993</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.349141430722087</v>
+        <v>5.181980761012022</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07222952315655026</v>
+        <v>0.0721478361412585</v>
       </c>
       <c r="C34">
-        <v>5326.835782588469</v>
+        <v>5274.23650984799</v>
       </c>
       <c r="D34">
-        <v>7158.179782588469</v>
+        <v>7180.37250984799</v>
       </c>
       <c r="E34">
-        <v>56.54399999999987</v>
+        <v>131.3359999999998</v>
       </c>
       <c r="F34">
-        <v>2393.344</v>
+        <v>2468.136</v>
       </c>
       <c r="G34">
         <v>562</v>
@@ -4075,28 +4075,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M34">
-        <v>129.9585792</v>
+        <v>134.0197848</v>
       </c>
       <c r="N34">
-        <v>543.4842779428571</v>
+        <v>539.4230723428572</v>
       </c>
       <c r="O34">
-        <v>108.6968555885714</v>
+        <v>107.8846144685714</v>
       </c>
       <c r="P34">
-        <v>434.7874223542857</v>
+        <v>431.5384578742857</v>
       </c>
       <c r="Q34">
-        <v>753.4874223542856</v>
+        <v>750.2384578742856</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0857775340537504</v>
+        <v>0.08628751662874402</v>
       </c>
       <c r="T34">
-        <v>0.7792365488525993</v>
+        <v>0.7891770584692929</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.181980761012022</v>
+        <v>5.024951040981355</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0721478361412585</v>
+        <v>0.07206614912596672</v>
       </c>
       <c r="C35">
-        <v>5274.23650984799</v>
+        <v>5221.775274673839</v>
       </c>
       <c r="D35">
-        <v>7180.37250984799</v>
+        <v>7202.703274673839</v>
       </c>
       <c r="E35">
-        <v>131.3359999999998</v>
+        <v>206.1280000000002</v>
       </c>
       <c r="F35">
-        <v>2468.136</v>
+        <v>2542.928</v>
       </c>
       <c r="G35">
         <v>562</v>
@@ -4157,28 +4157,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M35">
-        <v>134.0197848</v>
+        <v>138.0809904</v>
       </c>
       <c r="N35">
-        <v>539.4230723428572</v>
+        <v>535.3618667428572</v>
       </c>
       <c r="O35">
-        <v>107.8846144685714</v>
+        <v>107.0723733485714</v>
       </c>
       <c r="P35">
-        <v>431.5384578742857</v>
+        <v>428.2894933942857</v>
       </c>
       <c r="Q35">
-        <v>750.2384578742856</v>
+        <v>746.9894933942857</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08628751662874402</v>
+        <v>0.0868129532211617</v>
       </c>
       <c r="T35">
-        <v>0.7891770584692929</v>
+        <v>0.7994187956501284</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.024951040981355</v>
+        <v>4.877158363305432</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07206614912596672</v>
+        <v>0.07198446211067495</v>
       </c>
       <c r="C36">
-        <v>5221.775274673839</v>
+        <v>5169.453368963093</v>
       </c>
       <c r="D36">
-        <v>7202.703274673839</v>
+        <v>7225.173368963094</v>
       </c>
       <c r="E36">
-        <v>206.1280000000002</v>
+        <v>280.9200000000001</v>
       </c>
       <c r="F36">
-        <v>2542.928</v>
+        <v>2617.72</v>
       </c>
       <c r="G36">
         <v>562</v>
@@ -4239,28 +4239,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M36">
-        <v>138.0809904</v>
+        <v>142.142196</v>
       </c>
       <c r="N36">
-        <v>535.3618667428572</v>
+        <v>531.3006611428572</v>
       </c>
       <c r="O36">
-        <v>107.0723733485714</v>
+        <v>106.2601322285714</v>
       </c>
       <c r="P36">
-        <v>428.2894933942857</v>
+        <v>425.0405289142857</v>
       </c>
       <c r="Q36">
-        <v>746.9894933942857</v>
+        <v>743.7405289142857</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0868129532211617</v>
+        <v>0.08735455709334608</v>
       </c>
       <c r="T36">
-        <v>0.7994187956501284</v>
+        <v>0.8099756632057591</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.877158363305432</v>
+        <v>4.737810981496706</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07198446211067495</v>
+        <v>0.07190277509538318</v>
       </c>
       <c r="C37">
-        <v>5169.453368963093</v>
+        <v>5117.272100784503</v>
       </c>
       <c r="D37">
-        <v>7225.173368963094</v>
+        <v>7247.784100784503</v>
       </c>
       <c r="E37">
-        <v>280.9200000000001</v>
+        <v>355.712</v>
       </c>
       <c r="F37">
-        <v>2617.72</v>
+        <v>2692.512</v>
       </c>
       <c r="G37">
         <v>562</v>
@@ -4321,28 +4321,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M37">
-        <v>142.142196</v>
+        <v>146.2034016</v>
       </c>
       <c r="N37">
-        <v>531.3006611428572</v>
+        <v>527.2394555428572</v>
       </c>
       <c r="O37">
-        <v>106.2601322285714</v>
+        <v>105.4478911085714</v>
       </c>
       <c r="P37">
-        <v>425.0405289142857</v>
+        <v>421.7915644342858</v>
       </c>
       <c r="Q37">
-        <v>743.7405289142857</v>
+        <v>740.4915644342857</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08735455709334608</v>
+        <v>0.08791308608653621</v>
       </c>
       <c r="T37">
-        <v>0.8099756632057591</v>
+        <v>0.8208624328725033</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.737810981496706</v>
+        <v>4.606205120899576</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07190277509538316</v>
+        <v>0.07182108808009141</v>
       </c>
       <c r="C38">
-        <v>5117.272100784506</v>
+        <v>5065.232794632273</v>
       </c>
       <c r="D38">
-        <v>7247.784100784505</v>
+        <v>7270.536794632273</v>
       </c>
       <c r="E38">
-        <v>355.7119999999995</v>
+        <v>430.5039999999999</v>
       </c>
       <c r="F38">
-        <v>2692.512</v>
+        <v>2767.304</v>
       </c>
       <c r="G38">
         <v>562</v>
@@ -4403,28 +4403,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M38">
-        <v>146.2034016</v>
+        <v>150.2646072</v>
       </c>
       <c r="N38">
-        <v>527.2394555428572</v>
+        <v>523.1782499428572</v>
       </c>
       <c r="O38">
-        <v>105.4478911085714</v>
+        <v>104.6356499885714</v>
       </c>
       <c r="P38">
-        <v>421.7915644342858</v>
+        <v>418.5425999542857</v>
       </c>
       <c r="Q38">
-        <v>740.4915644342857</v>
+        <v>737.2425999542857</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0879130860865362</v>
+        <v>0.08848934615887524</v>
       </c>
       <c r="T38">
-        <v>0.8208624328725032</v>
+        <v>0.8320948142746994</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.606205120899576</v>
+        <v>4.481713090604993</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07182108808009141</v>
+        <v>0.07173940106479963</v>
       </c>
       <c r="C39">
-        <v>5065.232794632273</v>
+        <v>5013.336791684746</v>
       </c>
       <c r="D39">
-        <v>7270.536794632273</v>
+        <v>7293.432791684745</v>
       </c>
       <c r="E39">
-        <v>430.5039999999999</v>
+        <v>505.2959999999998</v>
       </c>
       <c r="F39">
-        <v>2767.304</v>
+        <v>2842.096</v>
       </c>
       <c r="G39">
         <v>562</v>
@@ -4485,28 +4485,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M39">
-        <v>150.2646072</v>
+        <v>154.3258128</v>
       </c>
       <c r="N39">
-        <v>523.1782499428572</v>
+        <v>519.1170443428572</v>
       </c>
       <c r="O39">
-        <v>104.6356499885714</v>
+        <v>103.8234088685714</v>
       </c>
       <c r="P39">
-        <v>418.5425999542857</v>
+        <v>415.2936354742857</v>
       </c>
       <c r="Q39">
-        <v>737.2425999542857</v>
+        <v>733.9936354742856</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08848934615887524</v>
+        <v>0.08908419526580585</v>
       </c>
       <c r="T39">
-        <v>0.8320948142746994</v>
+        <v>0.8436895305608375</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.481713090604993</v>
+        <v>4.363773272431176</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07173940106479963</v>
+        <v>0.07165771404950785</v>
       </c>
       <c r="C40">
-        <v>5013.336791684746</v>
+        <v>4961.585450067896</v>
       </c>
       <c r="D40">
-        <v>7293.432791684745</v>
+        <v>7316.473450067896</v>
       </c>
       <c r="E40">
-        <v>505.2959999999998</v>
+        <v>580.0879999999997</v>
       </c>
       <c r="F40">
-        <v>2842.096</v>
+        <v>2916.888</v>
       </c>
       <c r="G40">
         <v>562</v>
@@ -4567,28 +4567,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M40">
-        <v>154.3258128</v>
+        <v>158.3870184</v>
       </c>
       <c r="N40">
-        <v>519.1170443428572</v>
+        <v>515.0558387428572</v>
       </c>
       <c r="O40">
-        <v>103.8234088685714</v>
+        <v>103.0111677485714</v>
       </c>
       <c r="P40">
-        <v>415.2936354742857</v>
+        <v>412.0446709942858</v>
       </c>
       <c r="Q40">
-        <v>733.9936354742856</v>
+        <v>730.7446709942857</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08908419526580585</v>
+        <v>0.08969854762214402</v>
       </c>
       <c r="T40">
-        <v>0.8436895305608375</v>
+        <v>0.855664401479308</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.363773272431176</v>
+        <v>4.251881650061147</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07165771404950785</v>
+        <v>0.07189602703421608</v>
       </c>
       <c r="C41">
-        <v>4961.585450067896</v>
+        <v>4819.978274595477</v>
       </c>
       <c r="D41">
-        <v>7316.473450067896</v>
+        <v>7249.658274595477</v>
       </c>
       <c r="E41">
-        <v>580.0879999999997</v>
+        <v>654.8800000000001</v>
       </c>
       <c r="F41">
-        <v>2916.888</v>
+        <v>2991.68</v>
       </c>
       <c r="G41">
         <v>562</v>
@@ -4649,45 +4649,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M41">
-        <v>158.3870184</v>
+        <v>165.439904</v>
       </c>
       <c r="N41">
-        <v>515.0558387428572</v>
+        <v>508.0029531428572</v>
       </c>
       <c r="O41">
-        <v>103.0111677485714</v>
+        <v>101.6005906285714</v>
       </c>
       <c r="P41">
-        <v>412.0446709942858</v>
+        <v>406.4023625142858</v>
       </c>
       <c r="Q41">
-        <v>730.7446709942857</v>
+        <v>725.1023625142857</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08969854762214402</v>
+        <v>0.09033337839036013</v>
       </c>
       <c r="T41">
-        <v>0.855664401479308</v>
+        <v>0.8680384347617275</v>
       </c>
       <c r="U41">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.251881650061147</v>
+        <v>4.070619245178341</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07189602703421608</v>
+        <v>0.0718223400189243</v>
       </c>
       <c r="C42">
-        <v>4819.978274595477</v>
+        <v>4765.71500797425</v>
       </c>
       <c r="D42">
-        <v>7249.658274595477</v>
+        <v>7270.187007974249</v>
       </c>
       <c r="E42">
-        <v>654.8800000000001</v>
+        <v>729.672</v>
       </c>
       <c r="F42">
-        <v>2991.68</v>
+        <v>3066.472</v>
       </c>
       <c r="G42">
         <v>562</v>
@@ -4731,28 +4731,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M42">
-        <v>165.439904</v>
+        <v>169.5759016</v>
       </c>
       <c r="N42">
-        <v>508.0029531428572</v>
+        <v>503.8669555428572</v>
       </c>
       <c r="O42">
-        <v>101.6005906285714</v>
+        <v>100.7733911085714</v>
       </c>
       <c r="P42">
-        <v>406.4023625142858</v>
+        <v>403.0935644342857</v>
       </c>
       <c r="Q42">
-        <v>725.1023625142857</v>
+        <v>721.7935644342856</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09033337839036013</v>
+        <v>0.09098972884563442</v>
       </c>
       <c r="T42">
-        <v>0.8680384347617275</v>
+        <v>0.8808319267994833</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.070619245178341</v>
+        <v>3.971335848954479</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0718223400189243</v>
+        <v>0.07174865300363253</v>
       </c>
       <c r="C43">
-        <v>4765.71500797425</v>
+        <v>4711.568333230849</v>
       </c>
       <c r="D43">
-        <v>7270.187007974249</v>
+        <v>7290.832333230849</v>
       </c>
       <c r="E43">
-        <v>729.672</v>
+        <v>804.4639999999999</v>
       </c>
       <c r="F43">
-        <v>3066.472</v>
+        <v>3141.264</v>
       </c>
       <c r="G43">
         <v>562</v>
@@ -4813,28 +4813,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M43">
-        <v>169.5759016</v>
+        <v>173.7118992</v>
       </c>
       <c r="N43">
-        <v>503.8669555428572</v>
+        <v>499.7309579428572</v>
       </c>
       <c r="O43">
-        <v>100.7733911085714</v>
+        <v>99.94619158857144</v>
       </c>
       <c r="P43">
-        <v>403.0935644342857</v>
+        <v>399.7847663542858</v>
       </c>
       <c r="Q43">
-        <v>721.7935644342856</v>
+        <v>718.4847663542857</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09098972884563442</v>
+        <v>0.0916687120752285</v>
       </c>
       <c r="T43">
-        <v>0.8808319267994833</v>
+        <v>0.8940665737350928</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.971335848954479</v>
+        <v>3.876780233503182</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07174865300363253</v>
+        <v>0.07167496598834076</v>
       </c>
       <c r="C44">
-        <v>4711.568333230849</v>
+        <v>4657.539246460206</v>
       </c>
       <c r="D44">
-        <v>7290.832333230849</v>
+        <v>7311.595246460206</v>
       </c>
       <c r="E44">
-        <v>804.4639999999995</v>
+        <v>879.2559999999999</v>
       </c>
       <c r="F44">
-        <v>3141.264</v>
+        <v>3216.056</v>
       </c>
       <c r="G44">
         <v>562</v>
@@ -4895,28 +4895,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M44">
-        <v>173.7118992</v>
+        <v>177.8478968</v>
       </c>
       <c r="N44">
-        <v>499.7309579428572</v>
+        <v>495.5949603428572</v>
       </c>
       <c r="O44">
-        <v>99.94619158857145</v>
+        <v>99.11899206857144</v>
       </c>
       <c r="P44">
-        <v>399.7847663542858</v>
+        <v>396.4759682742857</v>
       </c>
       <c r="Q44">
-        <v>718.4847663542857</v>
+        <v>715.1759682742857</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09166871207522849</v>
+        <v>0.0923715192777908</v>
       </c>
       <c r="T44">
-        <v>0.8940665737350925</v>
+        <v>0.9077655942473901</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.876780233503183</v>
+        <v>3.78662255365427</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07167496598834076</v>
+        <v>0.07160127897304899</v>
       </c>
       <c r="C45">
-        <v>4657.539246460206</v>
+        <v>4603.628755136421</v>
       </c>
       <c r="D45">
-        <v>7311.595246460206</v>
+        <v>7332.476755136421</v>
       </c>
       <c r="E45">
-        <v>879.2559999999999</v>
+        <v>954.0479999999998</v>
       </c>
       <c r="F45">
-        <v>3216.056</v>
+        <v>3290.848</v>
       </c>
       <c r="G45">
         <v>562</v>
@@ -4977,28 +4977,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M45">
-        <v>177.8478968</v>
+        <v>181.9838944</v>
       </c>
       <c r="N45">
-        <v>495.5949603428572</v>
+        <v>491.4589627428572</v>
       </c>
       <c r="O45">
-        <v>99.11899206857144</v>
+        <v>98.29179254857144</v>
       </c>
       <c r="P45">
-        <v>396.4759682742857</v>
+        <v>393.1671701942857</v>
       </c>
       <c r="Q45">
-        <v>715.1759682742857</v>
+        <v>711.8671701942857</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0923715192777908</v>
+        <v>0.09309942673758746</v>
       </c>
       <c r="T45">
-        <v>0.9077655942473901</v>
+        <v>0.9219538654922695</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.78662255365427</v>
+        <v>3.700562950162128</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07160127897304899</v>
+        <v>0.07152759195775721</v>
       </c>
       <c r="C46">
-        <v>4603.628755136421</v>
+        <v>4549.837878275715</v>
       </c>
       <c r="D46">
-        <v>7332.476755136421</v>
+        <v>7353.477878275716</v>
       </c>
       <c r="E46">
-        <v>954.0479999999998</v>
+        <v>1028.84</v>
       </c>
       <c r="F46">
-        <v>3290.848</v>
+        <v>3365.64</v>
       </c>
       <c r="G46">
         <v>562</v>
@@ -5059,28 +5059,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M46">
-        <v>181.9838944</v>
+        <v>186.119892</v>
       </c>
       <c r="N46">
-        <v>491.4589627428572</v>
+        <v>487.3229651428572</v>
       </c>
       <c r="O46">
-        <v>98.29179254857144</v>
+        <v>97.46459302857144</v>
       </c>
       <c r="P46">
-        <v>393.1671701942857</v>
+        <v>389.8583721142858</v>
       </c>
       <c r="Q46">
-        <v>711.8671701942857</v>
+        <v>708.5583721142857</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09309942673758746</v>
+        <v>0.09385380355955855</v>
       </c>
       <c r="T46">
-        <v>0.9219538654922695</v>
+        <v>0.9366580738733264</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.700562950162128</v>
+        <v>3.618328217936303</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07152759195775721</v>
+        <v>0.07145390494246544</v>
       </c>
       <c r="C47">
-        <v>4549.837878275715</v>
+        <v>4496.167646602193</v>
       </c>
       <c r="D47">
-        <v>7353.477878275716</v>
+        <v>7374.599646602192</v>
       </c>
       <c r="E47">
-        <v>1028.84</v>
+        <v>1103.632</v>
       </c>
       <c r="F47">
-        <v>3365.64</v>
+        <v>3440.432</v>
       </c>
       <c r="G47">
         <v>562</v>
@@ -5141,28 +5141,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M47">
-        <v>186.119892</v>
+        <v>190.2558896</v>
       </c>
       <c r="N47">
-        <v>487.3229651428572</v>
+        <v>483.1869675428571</v>
       </c>
       <c r="O47">
-        <v>97.46459302857144</v>
+        <v>96.63739350857144</v>
       </c>
       <c r="P47">
-        <v>389.8583721142858</v>
+        <v>386.5495740342857</v>
       </c>
       <c r="Q47">
-        <v>708.5583721142857</v>
+        <v>705.2495740342856</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09385380355955855</v>
+        <v>0.09463612026382487</v>
       </c>
       <c r="T47">
-        <v>0.9366580738733264</v>
+        <v>0.9519068825647929</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.618328217936303</v>
+        <v>3.539668908850731</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07145390494246544</v>
+        <v>0.07138021792717367</v>
       </c>
       <c r="C48">
-        <v>4496.167646602193</v>
+        <v>4442.619102716481</v>
       </c>
       <c r="D48">
-        <v>7374.599646602192</v>
+        <v>7395.843102716482</v>
       </c>
       <c r="E48">
-        <v>1103.632</v>
+        <v>1178.424</v>
       </c>
       <c r="F48">
-        <v>3440.432</v>
+        <v>3515.224</v>
       </c>
       <c r="G48">
         <v>562</v>
@@ -5223,28 +5223,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M48">
-        <v>190.2558896</v>
+        <v>194.3918872</v>
       </c>
       <c r="N48">
-        <v>483.1869675428571</v>
+        <v>479.0509699428571</v>
       </c>
       <c r="O48">
-        <v>96.63739350857144</v>
+        <v>95.81019398857143</v>
       </c>
       <c r="P48">
-        <v>386.5495740342857</v>
+        <v>383.2407759542857</v>
       </c>
       <c r="Q48">
-        <v>705.2495740342856</v>
+        <v>701.9407759542856</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09463612026382487</v>
+        <v>0.09544795835315785</v>
       </c>
       <c r="T48">
-        <v>0.9519068825647929</v>
+        <v>0.9677311179993336</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.539668908850731</v>
+        <v>3.464356804407098</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07138021792717367</v>
+        <v>0.07130653091188188</v>
       </c>
       <c r="C49">
-        <v>4442.619102716481</v>
+        <v>4389.193301267285</v>
       </c>
       <c r="D49">
-        <v>7395.843102716482</v>
+        <v>7417.209301267286</v>
       </c>
       <c r="E49">
-        <v>1178.424</v>
+        <v>1253.216</v>
       </c>
       <c r="F49">
-        <v>3515.224</v>
+        <v>3590.016</v>
       </c>
       <c r="G49">
         <v>562</v>
@@ -5305,28 +5305,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M49">
-        <v>194.3918872</v>
+        <v>198.5278848</v>
       </c>
       <c r="N49">
-        <v>479.0509699428571</v>
+        <v>474.9149723428571</v>
       </c>
       <c r="O49">
-        <v>95.81019398857143</v>
+        <v>94.98299446857143</v>
       </c>
       <c r="P49">
-        <v>383.2407759542857</v>
+        <v>379.9319778742857</v>
       </c>
       <c r="Q49">
-        <v>701.9407759542856</v>
+        <v>698.6319778742857</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09544795835315785</v>
+        <v>0.09629102098438824</v>
       </c>
       <c r="T49">
-        <v>0.9677311179993336</v>
+        <v>0.9841639778736643</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.464356804407098</v>
+        <v>3.392182704315284</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07130653091188188</v>
+        <v>0.07123284389659011</v>
       </c>
       <c r="C50">
-        <v>4389.193301267286</v>
+        <v>4335.891309125905</v>
       </c>
       <c r="D50">
-        <v>7417.209301267286</v>
+        <v>7438.699309125905</v>
       </c>
       <c r="E50">
-        <v>1253.215999999999</v>
+        <v>1328.008</v>
       </c>
       <c r="F50">
-        <v>3590.016</v>
+        <v>3664.808</v>
       </c>
       <c r="G50">
         <v>562</v>
@@ -5387,28 +5387,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M50">
-        <v>198.5278848</v>
+        <v>202.6638824</v>
       </c>
       <c r="N50">
-        <v>474.9149723428572</v>
+        <v>470.7789747428571</v>
       </c>
       <c r="O50">
-        <v>94.98299446857145</v>
+        <v>94.15579494857144</v>
       </c>
       <c r="P50">
-        <v>379.9319778742857</v>
+        <v>376.6231797942857</v>
       </c>
       <c r="Q50">
-        <v>698.6319778742857</v>
+        <v>695.3231797942856</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09629102098438824</v>
+        <v>0.09716714489527473</v>
       </c>
       <c r="T50">
-        <v>0.9841639778736643</v>
+        <v>1.00124126362542</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.392182704315284</v>
+        <v>3.32295448585987</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07123284389659011</v>
+        <v>0.07115915688129834</v>
       </c>
       <c r="C51">
-        <v>4335.891309125905</v>
+        <v>4282.714205563834</v>
       </c>
       <c r="D51">
-        <v>7438.699309125905</v>
+        <v>7460.314205563834</v>
       </c>
       <c r="E51">
-        <v>1328.008</v>
+        <v>1402.8</v>
       </c>
       <c r="F51">
-        <v>3664.808</v>
+        <v>3739.6</v>
       </c>
       <c r="G51">
         <v>562</v>
@@ -5469,28 +5469,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M51">
-        <v>202.6638824</v>
+        <v>206.79988</v>
       </c>
       <c r="N51">
-        <v>470.7789747428571</v>
+        <v>466.6429771428571</v>
       </c>
       <c r="O51">
-        <v>94.15579494857144</v>
+        <v>93.32859542857143</v>
       </c>
       <c r="P51">
-        <v>376.6231797942857</v>
+        <v>373.3143817142857</v>
       </c>
       <c r="Q51">
-        <v>695.3231797942856</v>
+        <v>692.0143817142857</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09716714489527473</v>
+        <v>0.09807831376259668</v>
       </c>
       <c r="T51">
-        <v>1.00124126362542</v>
+        <v>1.019001640807245</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.32295448585987</v>
+        <v>3.256495396142673</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07115915688129834</v>
+        <v>0.07108546986600656</v>
       </c>
       <c r="C52">
-        <v>4282.714205563834</v>
+        <v>4229.663082433437</v>
       </c>
       <c r="D52">
-        <v>7460.314205563834</v>
+        <v>7482.055082433437</v>
       </c>
       <c r="E52">
-        <v>1402.8</v>
+        <v>1477.592</v>
       </c>
       <c r="F52">
-        <v>3739.6</v>
+        <v>3814.392</v>
       </c>
       <c r="G52">
         <v>562</v>
@@ -5551,28 +5551,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M52">
-        <v>206.79988</v>
+        <v>210.9358776</v>
       </c>
       <c r="N52">
-        <v>466.6429771428571</v>
+        <v>462.5069795428572</v>
       </c>
       <c r="O52">
-        <v>93.32859542857143</v>
+        <v>92.50139590857144</v>
       </c>
       <c r="P52">
-        <v>373.3143817142857</v>
+        <v>370.0055836342857</v>
       </c>
       <c r="Q52">
-        <v>692.0143817142857</v>
+        <v>688.7055836342856</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09807831376259668</v>
+        <v>0.09902667319593175</v>
       </c>
       <c r="T52">
-        <v>1.019001640807245</v>
+        <v>1.037486931343431</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.256495396142673</v>
+        <v>3.192642545237914</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07108546986600656</v>
+        <v>0.07101178285071479</v>
       </c>
       <c r="C53">
-        <v>4229.663082433437</v>
+        <v>4176.739044351786</v>
       </c>
       <c r="D53">
-        <v>7482.055082433437</v>
+        <v>7503.923044351786</v>
       </c>
       <c r="E53">
-        <v>1477.592</v>
+        <v>1552.384</v>
       </c>
       <c r="F53">
-        <v>3814.392</v>
+        <v>3889.184</v>
       </c>
       <c r="G53">
         <v>562</v>
@@ -5633,28 +5633,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M53">
-        <v>210.9358776</v>
+        <v>215.0718752</v>
       </c>
       <c r="N53">
-        <v>462.5069795428572</v>
+        <v>458.3709819428572</v>
       </c>
       <c r="O53">
-        <v>92.50139590857144</v>
+        <v>91.67419638857143</v>
       </c>
       <c r="P53">
-        <v>370.0055836342857</v>
+        <v>366.6967855542857</v>
       </c>
       <c r="Q53">
-        <v>688.7055836342856</v>
+        <v>685.3967855542857</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09902667319593175</v>
+        <v>0.1000145476056558</v>
       </c>
       <c r="T53">
-        <v>1.037486931343431</v>
+        <v>1.056742442318625</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.192642545237914</v>
+        <v>3.131245573214108</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07101178285071479</v>
+        <v>0.07093809583542302</v>
       </c>
       <c r="C54">
-        <v>4176.739044351786</v>
+        <v>4123.943208887775</v>
       </c>
       <c r="D54">
-        <v>7503.923044351786</v>
+        <v>7525.919208887775</v>
       </c>
       <c r="E54">
-        <v>1552.384</v>
+        <v>1627.176</v>
       </c>
       <c r="F54">
-        <v>3889.184</v>
+        <v>3963.976</v>
       </c>
       <c r="G54">
         <v>562</v>
@@ -5715,28 +5715,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M54">
-        <v>215.0718752</v>
+        <v>219.2078728</v>
       </c>
       <c r="N54">
-        <v>458.3709819428572</v>
+        <v>454.2349843428572</v>
       </c>
       <c r="O54">
-        <v>91.67419638857143</v>
+        <v>90.84699686857144</v>
       </c>
       <c r="P54">
-        <v>366.6967855542857</v>
+        <v>363.3879874742858</v>
       </c>
       <c r="Q54">
-        <v>685.3967855542857</v>
+        <v>682.0879874742857</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1000145476056558</v>
+        <v>0.1010444592243043</v>
       </c>
       <c r="T54">
-        <v>1.056742442318625</v>
+        <v>1.076817336739571</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.131245573214108</v>
+        <v>3.072165468059125</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07093809583542302</v>
+        <v>0.07086440882013124</v>
       </c>
       <c r="C55">
-        <v>4123.943208887775</v>
+        <v>4071.276706752481</v>
       </c>
       <c r="D55">
-        <v>7525.919208887775</v>
+        <v>7548.044706752481</v>
       </c>
       <c r="E55">
-        <v>1627.176</v>
+        <v>1701.968</v>
       </c>
       <c r="F55">
-        <v>3963.976</v>
+        <v>4038.768</v>
       </c>
       <c r="G55">
         <v>562</v>
@@ -5797,28 +5797,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M55">
-        <v>219.2078728</v>
+        <v>223.3438704</v>
       </c>
       <c r="N55">
-        <v>454.2349843428572</v>
+        <v>450.0989867428572</v>
       </c>
       <c r="O55">
-        <v>90.84699686857144</v>
+        <v>90.01979734857144</v>
       </c>
       <c r="P55">
-        <v>363.3879874742858</v>
+        <v>360.0791893942857</v>
       </c>
       <c r="Q55">
-        <v>682.0879874742857</v>
+        <v>678.7791893942856</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1010444592243043</v>
+        <v>0.102119149608981</v>
       </c>
       <c r="T55">
-        <v>1.076817336739571</v>
+        <v>1.097765052657081</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.072165468059125</v>
+        <v>3.015273514946919</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07086440882013124</v>
+        <v>0.07189072180483946</v>
       </c>
       <c r="C56">
-        <v>4071.276706752481</v>
+        <v>3699.572403994291</v>
       </c>
       <c r="D56">
-        <v>7548.044706752481</v>
+        <v>7251.132403994291</v>
       </c>
       <c r="E56">
-        <v>1701.968</v>
+        <v>1776.76</v>
       </c>
       <c r="F56">
-        <v>4038.768</v>
+        <v>4113.56</v>
       </c>
       <c r="G56">
         <v>562</v>
@@ -5879,45 +5879,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M56">
-        <v>223.3438704</v>
+        <v>237.763768</v>
       </c>
       <c r="N56">
-        <v>450.0989867428572</v>
+        <v>435.6790891428572</v>
       </c>
       <c r="O56">
-        <v>90.01979734857144</v>
+        <v>87.13581782857143</v>
       </c>
       <c r="P56">
-        <v>360.0791893942857</v>
+        <v>348.5432713142857</v>
       </c>
       <c r="Q56">
-        <v>678.7791893942856</v>
+        <v>667.2432713142857</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.102119149608981</v>
+        <v>0.1032416040107544</v>
       </c>
       <c r="T56">
-        <v>1.097765052657081</v>
+        <v>1.119643778170924</v>
       </c>
       <c r="U56">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.015273514946919</v>
+        <v>2.832403199224438</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07189072180483946</v>
+        <v>0.0718370347895477</v>
       </c>
       <c r="C57">
-        <v>3699.572403994291</v>
+        <v>3639.731862922023</v>
       </c>
       <c r="D57">
-        <v>7251.132403994291</v>
+        <v>7266.083862922022</v>
       </c>
       <c r="E57">
-        <v>1776.76</v>
+        <v>1851.552</v>
       </c>
       <c r="F57">
-        <v>4113.56</v>
+        <v>4188.352</v>
       </c>
       <c r="G57">
         <v>562</v>
@@ -5961,28 +5961,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M57">
-        <v>237.763768</v>
+        <v>242.0867456</v>
       </c>
       <c r="N57">
-        <v>435.6790891428572</v>
+        <v>431.3561115428572</v>
       </c>
       <c r="O57">
-        <v>87.13581782857143</v>
+        <v>86.27122230857145</v>
       </c>
       <c r="P57">
-        <v>348.5432713142857</v>
+        <v>345.0848892342858</v>
       </c>
       <c r="Q57">
-        <v>667.2432713142857</v>
+        <v>663.7848892342856</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1032416040107544</v>
+        <v>0.1044150790671539</v>
       </c>
       <c r="T57">
-        <v>1.119643778170924</v>
+        <v>1.142516991208124</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.832403199224438</v>
+        <v>2.781824570666859</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0718370347895477</v>
+        <v>0.07178334777425592</v>
       </c>
       <c r="C58">
-        <v>3639.731862922023</v>
+        <v>3579.95310751426</v>
       </c>
       <c r="D58">
-        <v>7266.083862922022</v>
+        <v>7281.09710751426</v>
       </c>
       <c r="E58">
-        <v>1851.552</v>
+        <v>1926.344</v>
       </c>
       <c r="F58">
-        <v>4188.352</v>
+        <v>4263.144</v>
       </c>
       <c r="G58">
         <v>562</v>
@@ -6043,28 +6043,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M58">
-        <v>242.0867456</v>
+        <v>246.4097232</v>
       </c>
       <c r="N58">
-        <v>431.3561115428572</v>
+        <v>427.0331339428571</v>
       </c>
       <c r="O58">
-        <v>86.27122230857145</v>
+        <v>85.40662678857143</v>
       </c>
       <c r="P58">
-        <v>345.0848892342858</v>
+        <v>341.6265071542857</v>
       </c>
       <c r="Q58">
-        <v>663.7848892342856</v>
+        <v>660.3265071542857</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1044150790671539</v>
+        <v>0.1056431343587347</v>
       </c>
       <c r="T58">
-        <v>1.142516991208124</v>
+        <v>1.166454074619147</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.781824570666859</v>
+        <v>2.733020630830598</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07178334777425592</v>
+        <v>0.07172966075896414</v>
       </c>
       <c r="C59">
-        <v>3579.95310751426</v>
+        <v>3520.236521550168</v>
       </c>
       <c r="D59">
-        <v>7281.09710751426</v>
+        <v>7296.172521550168</v>
       </c>
       <c r="E59">
-        <v>1926.344</v>
+        <v>2001.136</v>
       </c>
       <c r="F59">
-        <v>4263.144</v>
+        <v>4337.936000000001</v>
       </c>
       <c r="G59">
         <v>562</v>
@@ -6125,28 +6125,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M59">
-        <v>246.4097232</v>
+        <v>250.7327008000001</v>
       </c>
       <c r="N59">
-        <v>427.0331339428571</v>
+        <v>422.7101563428571</v>
       </c>
       <c r="O59">
-        <v>85.40662678857143</v>
+        <v>84.54203126857142</v>
       </c>
       <c r="P59">
-        <v>341.6265071542857</v>
+        <v>338.1681250742857</v>
       </c>
       <c r="Q59">
-        <v>660.3265071542857</v>
+        <v>656.8681250742857</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1056431343587347</v>
+        <v>0.1069296684737241</v>
       </c>
       <c r="T59">
-        <v>1.166454074619147</v>
+        <v>1.19153101914498</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.733020630830598</v>
+        <v>2.68589958547145</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07172966075896414</v>
+        <v>0.07167597374367238</v>
       </c>
       <c r="C60">
-        <v>3520.236521550169</v>
+        <v>3460.58249199395</v>
       </c>
       <c r="D60">
-        <v>7296.172521550168</v>
+        <v>7311.310491993951</v>
       </c>
       <c r="E60">
-        <v>2001.136</v>
+        <v>2075.928</v>
       </c>
       <c r="F60">
-        <v>4337.936</v>
+        <v>4412.728</v>
       </c>
       <c r="G60">
         <v>562</v>
@@ -6207,28 +6207,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M60">
-        <v>250.7327008</v>
+        <v>255.0556784</v>
       </c>
       <c r="N60">
-        <v>422.7101563428572</v>
+        <v>418.3871787428571</v>
       </c>
       <c r="O60">
-        <v>84.54203126857145</v>
+        <v>83.67743574857144</v>
       </c>
       <c r="P60">
-        <v>338.1681250742857</v>
+        <v>334.7097429942857</v>
       </c>
       <c r="Q60">
-        <v>656.8681250742857</v>
+        <v>653.4097429942856</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1069296684737241</v>
+        <v>0.1082789603504204</v>
       </c>
       <c r="T60">
-        <v>1.19153101914498</v>
+        <v>1.21783122925744</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.68589958547145</v>
+        <v>2.640375863683798</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07167597374367238</v>
+        <v>0.0716222867283806</v>
       </c>
       <c r="C61">
-        <v>3460.58249199395</v>
+        <v>3400.991409027965</v>
       </c>
       <c r="D61">
-        <v>7311.310491993951</v>
+        <v>7326.511409027965</v>
       </c>
       <c r="E61">
-        <v>2075.928</v>
+        <v>2150.719999999999</v>
       </c>
       <c r="F61">
-        <v>4412.728</v>
+        <v>4487.52</v>
       </c>
       <c r="G61">
         <v>562</v>
@@ -6289,28 +6289,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M61">
-        <v>255.0556784</v>
+        <v>259.378656</v>
       </c>
       <c r="N61">
-        <v>418.3871787428571</v>
+        <v>414.0642011428572</v>
       </c>
       <c r="O61">
-        <v>83.67743574857144</v>
+        <v>82.81284022857145</v>
       </c>
       <c r="P61">
-        <v>334.7097429942857</v>
+        <v>331.2513609142858</v>
       </c>
       <c r="Q61">
-        <v>653.4097429942856</v>
+        <v>649.9513609142857</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1082789603504204</v>
+        <v>0.1096957168209515</v>
       </c>
       <c r="T61">
-        <v>1.21783122925744</v>
+        <v>1.245446449875522</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.640375863683798</v>
+        <v>2.596369599289069</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0716222867283806</v>
+        <v>0.07156859971308883</v>
       </c>
       <c r="C62">
-        <v>3400.991409027965</v>
+        <v>3341.463666086217</v>
       </c>
       <c r="D62">
-        <v>7326.511409027965</v>
+        <v>7341.775666086217</v>
       </c>
       <c r="E62">
-        <v>2150.719999999999</v>
+        <v>2225.512</v>
       </c>
       <c r="F62">
-        <v>4487.52</v>
+        <v>4562.312</v>
       </c>
       <c r="G62">
         <v>562</v>
@@ -6371,28 +6371,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M62">
-        <v>259.378656</v>
+        <v>263.7016336</v>
       </c>
       <c r="N62">
-        <v>414.0642011428572</v>
+        <v>409.7412235428571</v>
       </c>
       <c r="O62">
-        <v>82.81284022857145</v>
+        <v>81.94824470857144</v>
       </c>
       <c r="P62">
-        <v>331.2513609142858</v>
+        <v>327.7929788342857</v>
       </c>
       <c r="Q62">
-        <v>649.9513609142857</v>
+        <v>646.4929788342856</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1096957168209515</v>
+        <v>0.1111851274694585</v>
       </c>
       <c r="T62">
-        <v>1.245446449875522</v>
+        <v>1.274477835653506</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.596369599289069</v>
+        <v>2.553806163235149</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07156859971308883</v>
+        <v>0.07151491269779706</v>
       </c>
       <c r="C63">
-        <v>3341.463666086217</v>
+        <v>3281.999659888338</v>
       </c>
       <c r="D63">
-        <v>7341.775666086217</v>
+        <v>7357.103659888338</v>
       </c>
       <c r="E63">
-        <v>2225.512</v>
+        <v>2300.304</v>
       </c>
       <c r="F63">
-        <v>4562.312</v>
+        <v>4637.104</v>
       </c>
       <c r="G63">
         <v>562</v>
@@ -6453,28 +6453,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M63">
-        <v>263.7016336</v>
+        <v>268.0246112</v>
       </c>
       <c r="N63">
-        <v>409.7412235428571</v>
+        <v>405.4182459428571</v>
       </c>
       <c r="O63">
-        <v>81.94824470857144</v>
+        <v>81.08364918857143</v>
       </c>
       <c r="P63">
-        <v>327.7929788342857</v>
+        <v>324.3345967542857</v>
       </c>
       <c r="Q63">
-        <v>646.4929788342856</v>
+        <v>643.0345967542856</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1111851274694585</v>
+        <v>0.1127529281520975</v>
       </c>
       <c r="T63">
-        <v>1.274477835653506</v>
+        <v>1.305037189104016</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.553806163235149</v>
+        <v>2.512615741247485</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07151491269779706</v>
+        <v>0.07322522568250527</v>
       </c>
       <c r="C64">
-        <v>3281.999659888338</v>
+        <v>2748.398311698433</v>
       </c>
       <c r="D64">
-        <v>7357.103659888338</v>
+        <v>6898.294311698432</v>
       </c>
       <c r="E64">
-        <v>2300.304</v>
+        <v>2375.096</v>
       </c>
       <c r="F64">
-        <v>4637.104</v>
+        <v>4711.896</v>
       </c>
       <c r="G64">
         <v>562</v>
@@ -6535,45 +6535,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M64">
-        <v>268.0246112</v>
+        <v>288.8392248</v>
       </c>
       <c r="N64">
-        <v>405.4182459428571</v>
+        <v>384.6036323428572</v>
       </c>
       <c r="O64">
-        <v>81.08364918857143</v>
+        <v>76.92072646857144</v>
       </c>
       <c r="P64">
-        <v>324.3345967542857</v>
+        <v>307.6829058742857</v>
       </c>
       <c r="Q64">
-        <v>643.0345967542856</v>
+        <v>626.3829058742856</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1127529281520975</v>
+        <v>0.1144054748175818</v>
       </c>
       <c r="T64">
-        <v>1.305037189104016</v>
+        <v>1.337248399497797</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.512615741247485</v>
+        <v>2.33154917795243</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07322522568250527</v>
+        <v>0.0731995386672135</v>
       </c>
       <c r="C65">
-        <v>2748.398311698433</v>
+        <v>2680.073449471221</v>
       </c>
       <c r="D65">
-        <v>6898.294311698432</v>
+        <v>6904.761449471221</v>
       </c>
       <c r="E65">
-        <v>2375.096</v>
+        <v>2449.888</v>
       </c>
       <c r="F65">
-        <v>4711.896</v>
+        <v>4786.688</v>
       </c>
       <c r="G65">
         <v>562</v>
@@ -6617,28 +6617,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M65">
-        <v>288.8392248</v>
+        <v>293.4239744</v>
       </c>
       <c r="N65">
-        <v>384.6036323428572</v>
+        <v>380.0188827428572</v>
       </c>
       <c r="O65">
-        <v>76.92072646857144</v>
+        <v>76.00377654857144</v>
       </c>
       <c r="P65">
-        <v>307.6829058742857</v>
+        <v>304.0151061942857</v>
       </c>
       <c r="Q65">
-        <v>626.3829058742856</v>
+        <v>622.7151061942857</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1144054748175818</v>
+        <v>0.1161498296311486</v>
       </c>
       <c r="T65">
-        <v>1.337248399497797</v>
+        <v>1.37124912158012</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.33154917795243</v>
+        <v>2.295118722046923</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0731995386672135</v>
+        <v>0.07317385165192172</v>
       </c>
       <c r="C66">
-        <v>2680.073449471221</v>
+        <v>2611.760724481326</v>
       </c>
       <c r="D66">
-        <v>6904.761449471221</v>
+        <v>6911.240724481327</v>
       </c>
       <c r="E66">
-        <v>2449.888</v>
+        <v>2524.68</v>
       </c>
       <c r="F66">
-        <v>4786.688</v>
+        <v>4861.48</v>
       </c>
       <c r="G66">
         <v>562</v>
@@ -6699,28 +6699,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M66">
-        <v>293.4239744</v>
+        <v>298.008724</v>
       </c>
       <c r="N66">
-        <v>380.0188827428572</v>
+        <v>375.4341331428571</v>
       </c>
       <c r="O66">
-        <v>76.00377654857144</v>
+        <v>75.08682662857143</v>
       </c>
       <c r="P66">
-        <v>304.0151061942857</v>
+        <v>300.3473065142857</v>
       </c>
       <c r="Q66">
-        <v>622.7151061942857</v>
+        <v>619.0473065142857</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1161498296311486</v>
+        <v>0.1179938618626335</v>
       </c>
       <c r="T66">
-        <v>1.37124912158012</v>
+        <v>1.407192742067148</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.295118722046923</v>
+        <v>2.259809203246201</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07317385165192172</v>
+        <v>0.07462656463662995</v>
       </c>
       <c r="C67">
-        <v>2611.760724481326</v>
+        <v>2188.677165377527</v>
       </c>
       <c r="D67">
-        <v>6911.240724481327</v>
+        <v>6562.949165377527</v>
       </c>
       <c r="E67">
-        <v>2524.68</v>
+        <v>2599.472</v>
       </c>
       <c r="F67">
-        <v>4861.48</v>
+        <v>4936.272</v>
       </c>
       <c r="G67">
         <v>562</v>
@@ -6781,45 +6781,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M67">
-        <v>298.008724</v>
+        <v>316.4150352</v>
       </c>
       <c r="N67">
-        <v>375.4341331428571</v>
+        <v>357.0278219428571</v>
       </c>
       <c r="O67">
-        <v>75.08682662857143</v>
+        <v>71.40556438857143</v>
       </c>
       <c r="P67">
-        <v>300.3473065142857</v>
+        <v>285.6222575542857</v>
       </c>
       <c r="Q67">
-        <v>619.0473065142857</v>
+        <v>604.3222575542857</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1179938618626335</v>
+        <v>0.1199463665783234</v>
       </c>
       <c r="T67">
-        <v>1.407192742067148</v>
+        <v>1.44525069317106</v>
       </c>
       <c r="U67">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.259809203246201</v>
+        <v>2.128352898013163</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07462656463662995</v>
+        <v>0.07462327762133819</v>
       </c>
       <c r="C68">
-        <v>2188.677165377527</v>
+        <v>2114.633606083994</v>
       </c>
       <c r="D68">
-        <v>6562.949165377527</v>
+        <v>6563.697606083994</v>
       </c>
       <c r="E68">
-        <v>2599.472</v>
+        <v>2674.264</v>
       </c>
       <c r="F68">
-        <v>4936.272</v>
+        <v>5011.064</v>
       </c>
       <c r="G68">
         <v>562</v>
@@ -6863,28 +6863,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M68">
-        <v>316.4150352</v>
+        <v>321.2092024</v>
       </c>
       <c r="N68">
-        <v>357.0278219428571</v>
+        <v>352.2336547428571</v>
       </c>
       <c r="O68">
-        <v>71.40556438857143</v>
+        <v>70.44673094857143</v>
       </c>
       <c r="P68">
-        <v>285.6222575542857</v>
+        <v>281.7869237942857</v>
       </c>
       <c r="Q68">
-        <v>604.3222575542857</v>
+        <v>600.4869237942856</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1199463665783234</v>
+        <v>0.122017204913146</v>
       </c>
       <c r="T68">
-        <v>1.44525069317106</v>
+        <v>1.485615186766119</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.128352898013163</v>
+        <v>2.096586436848788</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07462327762133819</v>
+        <v>0.0746199906060464</v>
       </c>
       <c r="C69">
-        <v>2114.633606083994</v>
+        <v>2040.590217514746</v>
       </c>
       <c r="D69">
-        <v>6563.697606083994</v>
+        <v>6564.446217514746</v>
       </c>
       <c r="E69">
-        <v>2674.264</v>
+        <v>2749.056</v>
       </c>
       <c r="F69">
-        <v>5011.064</v>
+        <v>5085.856000000001</v>
       </c>
       <c r="G69">
         <v>562</v>
@@ -6945,28 +6945,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M69">
-        <v>321.2092024</v>
+        <v>326.0033696</v>
       </c>
       <c r="N69">
-        <v>352.2336547428571</v>
+        <v>347.4394875428571</v>
       </c>
       <c r="O69">
-        <v>70.44673094857143</v>
+        <v>69.48789750857144</v>
       </c>
       <c r="P69">
-        <v>281.7869237942857</v>
+        <v>277.9515900342857</v>
       </c>
       <c r="Q69">
-        <v>600.4869237942856</v>
+        <v>596.6515900342856</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.122017204913146</v>
+        <v>0.124217470643895</v>
       </c>
       <c r="T69">
-        <v>1.485615186766119</v>
+        <v>1.528502461210868</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.096586436848788</v>
+        <v>2.065754283365718</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0746199906060464</v>
+        <v>0.07461670359075465</v>
       </c>
       <c r="C70">
-        <v>2040.590217514746</v>
+        <v>1966.546999728193</v>
       </c>
       <c r="D70">
-        <v>6564.446217514746</v>
+        <v>6565.194999728193</v>
       </c>
       <c r="E70">
-        <v>2749.056</v>
+        <v>2823.848</v>
       </c>
       <c r="F70">
-        <v>5085.856000000001</v>
+        <v>5160.648</v>
       </c>
       <c r="G70">
         <v>562</v>
@@ -7027,28 +7027,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M70">
-        <v>326.0033696</v>
+        <v>330.7975368</v>
       </c>
       <c r="N70">
-        <v>347.4394875428571</v>
+        <v>342.6453203428571</v>
       </c>
       <c r="O70">
-        <v>69.48789750857144</v>
+        <v>68.52906406857143</v>
       </c>
       <c r="P70">
-        <v>277.9515900342857</v>
+        <v>274.1162562742857</v>
       </c>
       <c r="Q70">
-        <v>596.6515900342856</v>
+        <v>592.8162562742857</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.124217470643895</v>
+        <v>0.1265596890024343</v>
       </c>
       <c r="T70">
-        <v>1.528502461210868</v>
+        <v>1.574156656587537</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.065754283365718</v>
+        <v>2.035815815490852</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07461670359075465</v>
+        <v>0.07461341657546286</v>
       </c>
       <c r="C71">
-        <v>1966.546999728193</v>
+        <v>1892.503952782793</v>
       </c>
       <c r="D71">
-        <v>6565.194999728193</v>
+        <v>6565.943952782794</v>
       </c>
       <c r="E71">
-        <v>2823.848</v>
+        <v>2898.64</v>
       </c>
       <c r="F71">
-        <v>5160.648</v>
+        <v>5235.440000000001</v>
       </c>
       <c r="G71">
         <v>562</v>
@@ -7109,28 +7109,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M71">
-        <v>330.7975368</v>
+        <v>335.591704</v>
       </c>
       <c r="N71">
-        <v>342.6453203428571</v>
+        <v>337.8511531428571</v>
       </c>
       <c r="O71">
-        <v>68.52906406857143</v>
+        <v>67.57023062857142</v>
       </c>
       <c r="P71">
-        <v>274.1162562742857</v>
+        <v>270.2809225142857</v>
       </c>
       <c r="Q71">
-        <v>592.8162562742857</v>
+        <v>588.9809225142856</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1265596890024343</v>
+        <v>0.1290580552515428</v>
       </c>
       <c r="T71">
-        <v>1.574156656587537</v>
+        <v>1.622854464989317</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.035815815490852</v>
+        <v>2.006732732412411</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07461341657546286</v>
+        <v>0.07904052956017109</v>
       </c>
       <c r="C72">
-        <v>1892.503952782793</v>
+        <v>943.2320297835886</v>
       </c>
       <c r="D72">
-        <v>6565.943952782794</v>
+        <v>5691.464029783589</v>
       </c>
       <c r="E72">
-        <v>2898.64</v>
+        <v>2973.432000000001</v>
       </c>
       <c r="F72">
-        <v>5235.440000000001</v>
+        <v>5310.232000000001</v>
       </c>
       <c r="G72">
         <v>562</v>
@@ -7191,45 +7191,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M72">
-        <v>335.591704</v>
+        <v>381.8056808000001</v>
       </c>
       <c r="N72">
-        <v>337.8511531428571</v>
+        <v>291.6371763428571</v>
       </c>
       <c r="O72">
-        <v>67.57023062857142</v>
+        <v>58.32743526857141</v>
       </c>
       <c r="P72">
-        <v>270.2809225142857</v>
+        <v>233.3097410742857</v>
       </c>
       <c r="Q72">
-        <v>588.9809225142856</v>
+        <v>552.0097410742856</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1290580552515428</v>
+        <v>0.1317287226212796</v>
       </c>
       <c r="T72">
-        <v>1.622854464989317</v>
+        <v>1.674910742936047</v>
       </c>
       <c r="U72">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.006732732412411</v>
+        <v>1.763836660920779</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07904052956017109</v>
+        <v>0.0813460425448793</v>
       </c>
       <c r="C73">
-        <v>943.2320297835895</v>
+        <v>499.2922067566324</v>
       </c>
       <c r="D73">
-        <v>5691.464029783589</v>
+        <v>5322.316206756632</v>
       </c>
       <c r="E73">
-        <v>2973.432</v>
+        <v>3048.223999999999</v>
       </c>
       <c r="F73">
-        <v>5310.232</v>
+        <v>5385.023999999999</v>
       </c>
       <c r="G73">
         <v>562</v>
@@ -7273,45 +7273,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M73">
-        <v>381.8056808</v>
+        <v>408.1848192</v>
       </c>
       <c r="N73">
-        <v>291.6371763428572</v>
+        <v>265.2580379428572</v>
       </c>
       <c r="O73">
-        <v>58.32743526857143</v>
+        <v>53.05160758857144</v>
       </c>
       <c r="P73">
-        <v>233.3097410742857</v>
+        <v>212.2064303542857</v>
       </c>
       <c r="Q73">
-        <v>552.0097410742857</v>
+        <v>530.9064303542857</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1317287226212796</v>
+        <v>0.1345901519459975</v>
       </c>
       <c r="T73">
-        <v>1.674910742936047</v>
+        <v>1.730685326450401</v>
       </c>
       <c r="U73">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.76383666092078</v>
+        <v>1.649847876417196</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0813460425448793</v>
+        <v>0.08143635552958754</v>
       </c>
       <c r="C74">
-        <v>499.2922067566324</v>
+        <v>411.0118953103583</v>
       </c>
       <c r="D74">
-        <v>5322.316206756632</v>
+        <v>5308.827895310358</v>
       </c>
       <c r="E74">
-        <v>3048.223999999999</v>
+        <v>3123.016</v>
       </c>
       <c r="F74">
-        <v>5385.023999999999</v>
+        <v>5459.816</v>
       </c>
       <c r="G74">
         <v>562</v>
@@ -7355,28 +7355,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M74">
-        <v>408.1848192</v>
+        <v>413.8540528</v>
       </c>
       <c r="N74">
-        <v>265.2580379428572</v>
+        <v>259.5888043428571</v>
       </c>
       <c r="O74">
-        <v>53.05160758857144</v>
+        <v>51.91776086857143</v>
       </c>
       <c r="P74">
-        <v>212.2064303542857</v>
+        <v>207.6710434742857</v>
       </c>
       <c r="Q74">
-        <v>530.9064303542857</v>
+        <v>526.3710434742857</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1345901519459975</v>
+        <v>0.1376635389984723</v>
       </c>
       <c r="T74">
-        <v>1.730685326450401</v>
+        <v>1.790591360595447</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.649847876417196</v>
+        <v>1.627247220575865</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08143635552958754</v>
+        <v>0.08152666851429577</v>
       </c>
       <c r="C75">
-        <v>411.0118953103583</v>
+        <v>322.7997777212822</v>
       </c>
       <c r="D75">
-        <v>5308.827895310358</v>
+        <v>5295.407777721282</v>
       </c>
       <c r="E75">
-        <v>3123.016</v>
+        <v>3197.808</v>
       </c>
       <c r="F75">
-        <v>5459.816</v>
+        <v>5534.608</v>
       </c>
       <c r="G75">
         <v>562</v>
@@ -7437,28 +7437,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M75">
-        <v>413.8540528</v>
+        <v>419.5232864000001</v>
       </c>
       <c r="N75">
-        <v>259.5888043428571</v>
+        <v>253.9195707428571</v>
       </c>
       <c r="O75">
-        <v>51.91776086857143</v>
+        <v>50.78391414857143</v>
       </c>
       <c r="P75">
-        <v>207.6710434742857</v>
+        <v>203.1356565942857</v>
       </c>
       <c r="Q75">
-        <v>526.3710434742857</v>
+        <v>521.8356565942856</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1376635389984723</v>
+        <v>0.1409733404395991</v>
       </c>
       <c r="T75">
-        <v>1.790591360595447</v>
+        <v>1.85510555121319</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.627247220575865</v>
+        <v>1.605257393270785</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08152666851429577</v>
+        <v>0.081616981499004</v>
       </c>
       <c r="C76">
-        <v>322.7997777212822</v>
+        <v>234.6553381343101</v>
       </c>
       <c r="D76">
-        <v>5295.407777721282</v>
+        <v>5282.05533813431</v>
       </c>
       <c r="E76">
-        <v>3197.808</v>
+        <v>3272.599999999999</v>
       </c>
       <c r="F76">
-        <v>5534.608</v>
+        <v>5609.4</v>
       </c>
       <c r="G76">
         <v>562</v>
@@ -7519,28 +7519,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M76">
-        <v>419.5232864000001</v>
+        <v>425.19252</v>
       </c>
       <c r="N76">
-        <v>253.9195707428571</v>
+        <v>248.2503371428572</v>
       </c>
       <c r="O76">
-        <v>50.78391414857143</v>
+        <v>49.65006742857144</v>
       </c>
       <c r="P76">
-        <v>203.1356565942857</v>
+        <v>198.6002697142857</v>
       </c>
       <c r="Q76">
-        <v>521.8356565942856</v>
+        <v>517.3002697142856</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1409733404395991</v>
+        <v>0.144547925996016</v>
       </c>
       <c r="T76">
-        <v>1.85510555121319</v>
+        <v>1.924780877080353</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.605257393270785</v>
+        <v>1.583853961360508</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.081616981499004</v>
+        <v>0.08170729448371222</v>
       </c>
       <c r="C77">
-        <v>234.6553381343101</v>
+        <v>146.5780658842004</v>
       </c>
       <c r="D77">
-        <v>5282.05533813431</v>
+        <v>5268.7700658842</v>
       </c>
       <c r="E77">
-        <v>3272.599999999999</v>
+        <v>3347.392</v>
       </c>
       <c r="F77">
-        <v>5609.4</v>
+        <v>5684.192</v>
       </c>
       <c r="G77">
         <v>562</v>
@@ -7601,28 +7601,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M77">
-        <v>425.19252</v>
+        <v>430.8617536</v>
       </c>
       <c r="N77">
-        <v>248.2503371428572</v>
+        <v>242.5811035428571</v>
       </c>
       <c r="O77">
-        <v>49.65006742857144</v>
+        <v>48.51622070857143</v>
       </c>
       <c r="P77">
-        <v>198.6002697142857</v>
+        <v>194.0648828342857</v>
       </c>
       <c r="Q77">
-        <v>517.3002697142856</v>
+        <v>512.7648828342856</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.144547925996016</v>
+        <v>0.1484203936821342</v>
       </c>
       <c r="T77">
-        <v>1.924780877080353</v>
+        <v>2.000262480103111</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.583853961360508</v>
+        <v>1.563013777658396</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08170729448371222</v>
+        <v>0.08179760746842045</v>
       </c>
       <c r="C78">
-        <v>146.5780658842004</v>
+        <v>58.56745543046964</v>
       </c>
       <c r="D78">
-        <v>5268.7700658842</v>
+        <v>5255.55145543047</v>
       </c>
       <c r="E78">
-        <v>3347.392</v>
+        <v>3422.184</v>
       </c>
       <c r="F78">
-        <v>5684.192</v>
+        <v>5758.984</v>
       </c>
       <c r="G78">
         <v>562</v>
@@ -7683,28 +7683,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M78">
-        <v>430.8617536</v>
+        <v>436.5309872000001</v>
       </c>
       <c r="N78">
-        <v>242.5811035428571</v>
+        <v>236.9118699428571</v>
       </c>
       <c r="O78">
-        <v>48.51622070857143</v>
+        <v>47.38237398857142</v>
       </c>
       <c r="P78">
-        <v>194.0648828342857</v>
+        <v>189.5294959542857</v>
       </c>
       <c r="Q78">
-        <v>512.7648828342856</v>
+        <v>508.2294959542856</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1484203936821342</v>
+        <v>0.1526295976887845</v>
       </c>
       <c r="T78">
-        <v>2.000262480103111</v>
+        <v>2.082307700780023</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.563013777658396</v>
+        <v>1.542714897429066</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08179760746842045</v>
+        <v>0.08188792045312866</v>
       </c>
       <c r="C79">
-        <v>58.56745543046964</v>
+        <v>-29.3769937067409</v>
       </c>
       <c r="D79">
-        <v>5255.55145543047</v>
+        <v>5242.399006293259</v>
       </c>
       <c r="E79">
-        <v>3422.184</v>
+        <v>3496.976</v>
       </c>
       <c r="F79">
-        <v>5758.984</v>
+        <v>5833.776</v>
       </c>
       <c r="G79">
         <v>562</v>
@@ -7765,28 +7765,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M79">
-        <v>436.5309872000001</v>
+        <v>442.2002208</v>
       </c>
       <c r="N79">
-        <v>236.9118699428571</v>
+        <v>231.2426363428572</v>
       </c>
       <c r="O79">
-        <v>47.38237398857142</v>
+        <v>46.24852726857144</v>
       </c>
       <c r="P79">
-        <v>189.5294959542857</v>
+        <v>184.9941090742857</v>
       </c>
       <c r="Q79">
-        <v>508.2294959542856</v>
+        <v>503.6941090742857</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1526295976887845</v>
+        <v>0.1572214566051303</v>
       </c>
       <c r="T79">
-        <v>2.082307700780023</v>
+        <v>2.171811577882109</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.542714897429066</v>
+        <v>1.522936501308181</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08188792045312866</v>
+        <v>0.08197823343783689</v>
       </c>
       <c r="C80">
-        <v>-29.3769937067409</v>
+        <v>-117.2557770098383</v>
       </c>
       <c r="D80">
-        <v>5242.399006293259</v>
+        <v>5229.312222990162</v>
       </c>
       <c r="E80">
-        <v>3496.976</v>
+        <v>3571.768</v>
       </c>
       <c r="F80">
-        <v>5833.776</v>
+        <v>5908.568</v>
       </c>
       <c r="G80">
         <v>562</v>
@@ -7847,28 +7847,28 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M80">
-        <v>442.2002208</v>
+        <v>447.8694544000001</v>
       </c>
       <c r="N80">
-        <v>231.2426363428572</v>
+        <v>225.5734027428571</v>
       </c>
       <c r="O80">
-        <v>46.24852726857144</v>
+        <v>45.11468054857143</v>
       </c>
       <c r="P80">
-        <v>184.9941090742857</v>
+        <v>180.4587221942857</v>
       </c>
       <c r="Q80">
-        <v>503.6941090742857</v>
+        <v>499.1587221942856</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1572214566051303</v>
+        <v>0.1622506354182709</v>
       </c>
       <c r="T80">
-        <v>2.171811577882109</v>
+        <v>2.269839633755822</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.522936501308181</v>
+        <v>1.503658824076432</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08197823343783689</v>
+        <v>0.09115654642254511</v>
       </c>
       <c r="C81">
-        <v>-117.2557770098383</v>
+        <v>-1250.247046200819</v>
       </c>
       <c r="D81">
-        <v>5229.312222990162</v>
+        <v>4171.112953799182</v>
       </c>
       <c r="E81">
-        <v>3571.768</v>
+        <v>3646.56</v>
       </c>
       <c r="F81">
-        <v>5908.568</v>
+        <v>5983.360000000001</v>
       </c>
       <c r="G81">
         <v>562</v>
@@ -7929,45 +7929,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M81">
-        <v>447.8694544000001</v>
+        <v>538.5024000000001</v>
       </c>
       <c r="N81">
-        <v>225.5734027428571</v>
+        <v>134.9404571428571</v>
       </c>
       <c r="O81">
-        <v>45.11468054857143</v>
+        <v>26.98809142857142</v>
       </c>
       <c r="P81">
-        <v>180.4587221942857</v>
+        <v>107.9523657142857</v>
       </c>
       <c r="Q81">
-        <v>499.1587221942856</v>
+        <v>426.6523657142856</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1622506354182709</v>
+        <v>0.1677827321127256</v>
       </c>
       <c r="T81">
-        <v>2.269839633755822</v>
+        <v>2.377670495216906</v>
       </c>
       <c r="U81">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V81">
         <v>0.2</v>
       </c>
       <c r="W81">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.503658824076432</v>
+        <v>1.250584690324235</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09115654642254511</v>
+        <v>0.1113930740190481</v>
       </c>
       <c r="C82">
-        <v>-1250.247046200819</v>
+        <v>-2611.895069645855</v>
       </c>
       <c r="D82">
-        <v>4171.112953799182</v>
+        <v>2884.256930354145</v>
       </c>
       <c r="E82">
-        <v>3646.56</v>
+        <v>3721.352</v>
       </c>
       <c r="F82">
-        <v>5983.360000000001</v>
+        <v>6058.152</v>
       </c>
       <c r="G82">
         <v>562</v>
@@ -8011,45 +8011,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M82">
-        <v>538.5024000000001</v>
+        <v>718.4968272000001</v>
       </c>
       <c r="N82">
-        <v>134.9404571428571</v>
+        <v>-45.05397005714292</v>
       </c>
       <c r="O82">
-        <v>26.98809142857142</v>
+        <v>-9.010794011428585</v>
       </c>
       <c r="P82">
-        <v>107.9523657142857</v>
+        <v>-36.04317604571433</v>
       </c>
       <c r="Q82">
-        <v>426.6523657142856</v>
+        <v>282.6568239542856</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1677827321127256</v>
+        <v>0.175449966103774</v>
       </c>
       <c r="T82">
-        <v>2.377670495216906</v>
+        <v>2.527119156717562</v>
       </c>
       <c r="U82">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V82">
-        <v>0.2</v>
+        <v>0.1874588256060311</v>
       </c>
       <c r="W82">
-        <v>0.07199999999999999</v>
+        <v>0.09636738328312473</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.250584690324235</v>
+        <v>0.9372941280301552</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1113930740190481</v>
+        <v>0.1121210740190481</v>
       </c>
       <c r="C83">
-        <v>-2611.895069645855</v>
+        <v>-2718.347278355604</v>
       </c>
       <c r="D83">
-        <v>2884.256930354145</v>
+        <v>2852.596721644396</v>
       </c>
       <c r="E83">
-        <v>3721.352</v>
+        <v>3796.144</v>
       </c>
       <c r="F83">
-        <v>6058.152</v>
+        <v>6132.944</v>
       </c>
       <c r="G83">
         <v>562</v>
@@ -8093,37 +8093,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M83">
-        <v>718.4968272000001</v>
+        <v>727.3671584000001</v>
       </c>
       <c r="N83">
-        <v>-45.05397005714292</v>
+        <v>-53.92430125714293</v>
       </c>
       <c r="O83">
-        <v>-9.010794011428585</v>
+        <v>-10.78486025142859</v>
       </c>
       <c r="P83">
-        <v>-36.04317604571433</v>
+        <v>-43.13944100571435</v>
       </c>
       <c r="Q83">
-        <v>282.6568239542856</v>
+        <v>275.5605589942856</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.175449966103774</v>
+        <v>0.1826527419984281</v>
       </c>
       <c r="T83">
-        <v>2.527119156717562</v>
+        <v>2.667514665424093</v>
       </c>
       <c r="U83">
         <v>0.1186</v>
       </c>
       <c r="V83">
-        <v>0.1874588256060311</v>
+        <v>0.1851727423669331</v>
       </c>
       <c r="W83">
-        <v>0.09636738328312473</v>
+        <v>0.09663851275528174</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9372941280301552</v>
+        <v>0.9258637118346655</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1121210740190481</v>
+        <v>0.1128490740190481</v>
       </c>
       <c r="C84">
-        <v>-2718.347278355604</v>
+        <v>-2824.111971770687</v>
       </c>
       <c r="D84">
-        <v>2852.596721644396</v>
+        <v>2821.624028229314</v>
       </c>
       <c r="E84">
-        <v>3796.144</v>
+        <v>3870.936000000001</v>
       </c>
       <c r="F84">
-        <v>6132.944</v>
+        <v>6207.736000000001</v>
       </c>
       <c r="G84">
         <v>562</v>
@@ -8175,37 +8175,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M84">
-        <v>727.3671584000001</v>
+        <v>736.2374896000001</v>
       </c>
       <c r="N84">
-        <v>-53.92430125714293</v>
+        <v>-62.79463245714294</v>
       </c>
       <c r="O84">
-        <v>-10.78486025142859</v>
+        <v>-12.55892649142859</v>
       </c>
       <c r="P84">
-        <v>-43.13944100571435</v>
+        <v>-50.23570596571435</v>
       </c>
       <c r="Q84">
-        <v>275.5605589942856</v>
+        <v>268.4642940342856</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1826527419984281</v>
+        <v>0.1907029032924533</v>
       </c>
       <c r="T84">
-        <v>2.667514665424093</v>
+        <v>2.824427292801981</v>
       </c>
       <c r="U84">
         <v>0.1186</v>
       </c>
       <c r="V84">
-        <v>0.1851727423669331</v>
+        <v>0.182941745470946</v>
       </c>
       <c r="W84">
-        <v>0.09663851275528174</v>
+        <v>0.09690310898714581</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9258637118346655</v>
+        <v>0.9147087273547297</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1128490740190481</v>
+        <v>0.1135770740190481</v>
       </c>
       <c r="C85">
-        <v>-2824.111971770687</v>
+        <v>-2929.21130389266</v>
       </c>
       <c r="D85">
-        <v>2821.624028229314</v>
+        <v>2791.31669610734</v>
       </c>
       <c r="E85">
-        <v>3870.936000000001</v>
+        <v>3945.728</v>
       </c>
       <c r="F85">
-        <v>6207.736000000001</v>
+        <v>6282.528</v>
       </c>
       <c r="G85">
         <v>562</v>
@@ -8257,37 +8257,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M85">
-        <v>736.2374896000001</v>
+        <v>745.1078208000001</v>
       </c>
       <c r="N85">
-        <v>-62.79463245714294</v>
+        <v>-71.66496365714295</v>
       </c>
       <c r="O85">
-        <v>-12.55892649142859</v>
+        <v>-14.33299273142859</v>
       </c>
       <c r="P85">
-        <v>-50.23570596571435</v>
+        <v>-57.33197092571436</v>
       </c>
       <c r="Q85">
-        <v>268.4642940342856</v>
+        <v>261.3680290742856</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1907029032924533</v>
+        <v>0.1997593347482316</v>
       </c>
       <c r="T85">
-        <v>2.824427292801981</v>
+        <v>3.000953998602105</v>
       </c>
       <c r="U85">
         <v>0.1186</v>
       </c>
       <c r="V85">
-        <v>0.182941745470946</v>
+        <v>0.1807638675486728</v>
       </c>
       <c r="W85">
-        <v>0.09690310898714581</v>
+        <v>0.09716140530872741</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9147087273547297</v>
+        <v>0.9038193377433639</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1135770740190481</v>
+        <v>0.1143050740190481</v>
       </c>
       <c r="C86">
-        <v>-2929.21130389266</v>
+        <v>-3033.666487005216</v>
       </c>
       <c r="D86">
-        <v>2791.316696107339</v>
+        <v>2761.653512994784</v>
       </c>
       <c r="E86">
-        <v>3945.727999999999</v>
+        <v>4020.52</v>
       </c>
       <c r="F86">
-        <v>6282.527999999999</v>
+        <v>6357.32</v>
       </c>
       <c r="G86">
         <v>562</v>
@@ -8339,37 +8339,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M86">
-        <v>745.1078208</v>
+        <v>753.978152</v>
       </c>
       <c r="N86">
-        <v>-71.66496365714283</v>
+        <v>-80.53529485714284</v>
       </c>
       <c r="O86">
-        <v>-14.33299273142857</v>
+        <v>-16.10705897142857</v>
       </c>
       <c r="P86">
-        <v>-57.33197092571427</v>
+        <v>-64.42823588571427</v>
       </c>
       <c r="Q86">
-        <v>261.3680290742857</v>
+        <v>254.2717641142856</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1997593347482315</v>
+        <v>0.2100232903981136</v>
       </c>
       <c r="T86">
-        <v>3.000953998602104</v>
+        <v>3.201017598508911</v>
       </c>
       <c r="U86">
         <v>0.1186</v>
       </c>
       <c r="V86">
-        <v>0.1807638675486728</v>
+        <v>0.1786372338128061</v>
       </c>
       <c r="W86">
-        <v>0.09716140530872741</v>
+        <v>0.09741362406980121</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9038193377433641</v>
+        <v>0.8931861690640304</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1143050740190481</v>
+        <v>0.1150330740190481</v>
       </c>
       <c r="C87">
-        <v>-3033.666487005216</v>
+        <v>-3137.497841185952</v>
       </c>
       <c r="D87">
-        <v>2761.653512994784</v>
+        <v>2732.614158814048</v>
       </c>
       <c r="E87">
-        <v>4020.52</v>
+        <v>4095.312</v>
       </c>
       <c r="F87">
-        <v>6357.32</v>
+        <v>6432.112</v>
       </c>
       <c r="G87">
         <v>562</v>
@@ -8421,37 +8421,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M87">
-        <v>753.978152</v>
+        <v>762.8484832</v>
       </c>
       <c r="N87">
-        <v>-80.53529485714284</v>
+        <v>-89.40562605714285</v>
       </c>
       <c r="O87">
-        <v>-16.10705897142857</v>
+        <v>-17.88112521142857</v>
       </c>
       <c r="P87">
-        <v>-64.42823588571427</v>
+        <v>-71.52450084571429</v>
       </c>
       <c r="Q87">
-        <v>254.2717641142856</v>
+        <v>247.1754991542857</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2100232903981136</v>
+        <v>0.2217535254265503</v>
       </c>
       <c r="T87">
-        <v>3.201017598508911</v>
+        <v>3.429661712688118</v>
       </c>
       <c r="U87">
         <v>0.1186</v>
       </c>
       <c r="V87">
-        <v>0.1786372338128061</v>
+        <v>0.1765600566754479</v>
       </c>
       <c r="W87">
-        <v>0.09741362406980121</v>
+        <v>0.0976599772782919</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8931861690640304</v>
+        <v>0.8828002833772393</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1150330740190481</v>
+        <v>0.1157610740190481</v>
       </c>
       <c r="C88">
-        <v>-3137.497841185952</v>
+        <v>-3240.724840726908</v>
       </c>
       <c r="D88">
-        <v>2732.614158814048</v>
+        <v>2704.179159273091</v>
       </c>
       <c r="E88">
-        <v>4095.312</v>
+        <v>4170.103999999999</v>
       </c>
       <c r="F88">
-        <v>6432.112</v>
+        <v>6506.904</v>
       </c>
       <c r="G88">
         <v>562</v>
@@ -8503,37 +8503,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M88">
-        <v>762.8484832</v>
+        <v>771.7188144</v>
       </c>
       <c r="N88">
-        <v>-89.40562605714285</v>
+        <v>-98.27595725714286</v>
       </c>
       <c r="O88">
-        <v>-17.88112521142857</v>
+        <v>-19.65519145142857</v>
       </c>
       <c r="P88">
-        <v>-71.52450084571429</v>
+        <v>-78.62076580571429</v>
       </c>
       <c r="Q88">
-        <v>247.1754991542857</v>
+        <v>240.0792341942856</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2217535254265503</v>
+        <v>0.2352884119978234</v>
       </c>
       <c r="T88">
-        <v>3.429661712688118</v>
+        <v>3.693481844433358</v>
       </c>
       <c r="U88">
         <v>0.1186</v>
       </c>
       <c r="V88">
-        <v>0.1765600566754479</v>
+        <v>0.1745306307366496</v>
       </c>
       <c r="W88">
-        <v>0.0976599772782919</v>
+        <v>0.09790066719463336</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8828002833772393</v>
+        <v>0.872653153683248</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1157610740190481</v>
+        <v>0.1164890740190481</v>
       </c>
       <c r="C89">
-        <v>-3240.724840726908</v>
+        <v>-3343.366157686703</v>
       </c>
       <c r="D89">
-        <v>2704.179159273091</v>
+        <v>2676.329842313296</v>
       </c>
       <c r="E89">
-        <v>4170.103999999999</v>
+        <v>4244.896</v>
       </c>
       <c r="F89">
-        <v>6506.904</v>
+        <v>6581.696</v>
       </c>
       <c r="G89">
         <v>562</v>
@@ -8585,37 +8585,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M89">
-        <v>771.7188144</v>
+        <v>780.5891456000001</v>
       </c>
       <c r="N89">
-        <v>-98.27595725714286</v>
+        <v>-107.1462884571429</v>
       </c>
       <c r="O89">
-        <v>-19.65519145142857</v>
+        <v>-21.42925769142857</v>
       </c>
       <c r="P89">
-        <v>-78.62076580571429</v>
+        <v>-85.7170307657143</v>
       </c>
       <c r="Q89">
-        <v>240.0792341942856</v>
+        <v>232.9829692342856</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2352884119978234</v>
+        <v>0.2510791129976421</v>
       </c>
       <c r="T89">
-        <v>3.693481844433358</v>
+        <v>4.001271998136139</v>
       </c>
       <c r="U89">
         <v>0.1186</v>
       </c>
       <c r="V89">
-        <v>0.1745306307366496</v>
+        <v>0.1725473281146422</v>
       </c>
       <c r="W89">
-        <v>0.09790066719463336</v>
+        <v>0.09813588688560344</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.872653153683248</v>
+        <v>0.8627366405732111</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1164890740190481</v>
+        <v>0.1172170740190481</v>
       </c>
       <c r="C90">
-        <v>-3343.366157686703</v>
+        <v>-3445.43970277891</v>
       </c>
       <c r="D90">
-        <v>2676.329842313296</v>
+        <v>2649.04829722109</v>
       </c>
       <c r="E90">
-        <v>4244.896</v>
+        <v>4319.688</v>
       </c>
       <c r="F90">
-        <v>6581.696</v>
+        <v>6656.488</v>
       </c>
       <c r="G90">
         <v>562</v>
@@ -8667,37 +8667,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M90">
-        <v>780.5891456000001</v>
+        <v>789.4594768000001</v>
       </c>
       <c r="N90">
-        <v>-107.1462884571429</v>
+        <v>-116.0166196571429</v>
       </c>
       <c r="O90">
-        <v>-21.42925769142857</v>
+        <v>-23.20332393142858</v>
       </c>
       <c r="P90">
-        <v>-85.7170307657143</v>
+        <v>-92.81329572571431</v>
       </c>
       <c r="Q90">
-        <v>232.9829692342856</v>
+        <v>225.8867042742856</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2510791129976421</v>
+        <v>0.2697408505428823</v>
       </c>
       <c r="T90">
-        <v>4.001271998136139</v>
+        <v>4.365023997966698</v>
       </c>
       <c r="U90">
         <v>0.1186</v>
       </c>
       <c r="V90">
-        <v>0.1725473281146422</v>
+        <v>0.1706085940908822</v>
       </c>
       <c r="W90">
-        <v>0.09813588688560344</v>
+        <v>0.09836582074082138</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8627366405732111</v>
+        <v>0.8530429704544109</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1172170740190481</v>
+        <v>0.1179450740190481</v>
       </c>
       <c r="C91">
-        <v>-3445.43970277891</v>
+        <v>-3546.962663784892</v>
       </c>
       <c r="D91">
-        <v>2649.04829722109</v>
+        <v>2622.317336215107</v>
       </c>
       <c r="E91">
-        <v>4319.688</v>
+        <v>4394.48</v>
       </c>
       <c r="F91">
-        <v>6656.488</v>
+        <v>6731.28</v>
       </c>
       <c r="G91">
         <v>562</v>
@@ -8749,37 +8749,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M91">
-        <v>789.4594768000001</v>
+        <v>798.3298080000001</v>
       </c>
       <c r="N91">
-        <v>-116.0166196571429</v>
+        <v>-124.8869508571429</v>
       </c>
       <c r="O91">
-        <v>-23.20332393142858</v>
+        <v>-24.97739017142858</v>
       </c>
       <c r="P91">
-        <v>-92.81329572571431</v>
+        <v>-99.90956068571431</v>
       </c>
       <c r="Q91">
-        <v>225.8867042742856</v>
+        <v>218.7904393142856</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2697408505428823</v>
+        <v>0.2921349355971705</v>
       </c>
       <c r="T91">
-        <v>4.365023997966698</v>
+        <v>4.801526397763367</v>
       </c>
       <c r="U91">
         <v>0.1186</v>
       </c>
       <c r="V91">
-        <v>0.1706085940908822</v>
+        <v>0.1687129430454279</v>
       </c>
       <c r="W91">
-        <v>0.09836582074082138</v>
+        <v>0.09859064495481225</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8530429704544109</v>
+        <v>0.8435647152271397</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1179450740190481</v>
+        <v>0.1186730740190481</v>
       </c>
       <c r="C92">
-        <v>-3546.962663784892</v>
+        <v>-3647.951541664171</v>
       </c>
       <c r="D92">
-        <v>2622.317336215107</v>
+        <v>2596.120458335829</v>
       </c>
       <c r="E92">
-        <v>4394.48</v>
+        <v>4469.272</v>
       </c>
       <c r="F92">
-        <v>6731.28</v>
+        <v>6806.072</v>
       </c>
       <c r="G92">
         <v>562</v>
@@ -8831,37 +8831,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M92">
-        <v>798.3298080000001</v>
+        <v>807.2001392000001</v>
       </c>
       <c r="N92">
-        <v>-124.8869508571429</v>
+        <v>-133.7572820571429</v>
       </c>
       <c r="O92">
-        <v>-24.97739017142858</v>
+        <v>-26.75145641142858</v>
       </c>
       <c r="P92">
-        <v>-99.90956068571431</v>
+        <v>-107.0058256457143</v>
       </c>
       <c r="Q92">
-        <v>218.7904393142856</v>
+        <v>211.6941743542856</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2921349355971705</v>
+        <v>0.3195054839968561</v>
       </c>
       <c r="T92">
-        <v>4.801526397763367</v>
+        <v>5.335029330848186</v>
       </c>
       <c r="U92">
         <v>0.1186</v>
       </c>
       <c r="V92">
-        <v>0.1687129430454279</v>
+        <v>0.1668589546603134</v>
       </c>
       <c r="W92">
-        <v>0.09859064495481225</v>
+        <v>0.09881052797728684</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8435647152271397</v>
+        <v>0.8342947733015668</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1186730740190481</v>
+        <v>0.1194010740190481</v>
       </c>
       <c r="C93">
-        <v>-3647.951541664171</v>
+        <v>-3748.422184521738</v>
       </c>
       <c r="D93">
-        <v>2596.120458335829</v>
+        <v>2570.441815478262</v>
       </c>
       <c r="E93">
-        <v>4469.272</v>
+        <v>4544.064</v>
       </c>
       <c r="F93">
-        <v>6806.072</v>
+        <v>6880.864</v>
       </c>
       <c r="G93">
         <v>562</v>
@@ -8913,37 +8913,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M93">
-        <v>807.2001392000001</v>
+        <v>816.0704704000001</v>
       </c>
       <c r="N93">
-        <v>-133.7572820571429</v>
+        <v>-142.6276132571429</v>
       </c>
       <c r="O93">
-        <v>-26.75145641142858</v>
+        <v>-28.52552265142858</v>
       </c>
       <c r="P93">
-        <v>-107.0058256457143</v>
+        <v>-114.1020906057143</v>
       </c>
       <c r="Q93">
-        <v>211.6941743542856</v>
+        <v>204.5979093942856</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3195054839968561</v>
+        <v>0.3537186694964632</v>
       </c>
       <c r="T93">
-        <v>5.335029330848186</v>
+        <v>6.001907997204211</v>
       </c>
       <c r="U93">
         <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.1668589546603134</v>
+        <v>0.1650452703705273</v>
       </c>
       <c r="W93">
-        <v>0.09881052797728684</v>
+        <v>0.09902563093405548</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8342947733015668</v>
+        <v>0.8252263518526366</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1194010740190481</v>
+        <v>0.1201290740190481</v>
       </c>
       <c r="C94">
-        <v>-3748.422184521738</v>
+        <v>-3848.389819579275</v>
       </c>
       <c r="D94">
-        <v>2570.441815478262</v>
+        <v>2545.266180420725</v>
       </c>
       <c r="E94">
-        <v>4544.064</v>
+        <v>4618.856</v>
       </c>
       <c r="F94">
-        <v>6880.864</v>
+        <v>6955.656</v>
       </c>
       <c r="G94">
         <v>562</v>
@@ -8995,37 +8995,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M94">
-        <v>816.0704704000001</v>
+        <v>824.9408016000001</v>
       </c>
       <c r="N94">
-        <v>-142.6276132571429</v>
+        <v>-151.4979444571429</v>
       </c>
       <c r="O94">
-        <v>-28.52552265142858</v>
+        <v>-30.29958889142858</v>
       </c>
       <c r="P94">
-        <v>-114.1020906057143</v>
+        <v>-121.1983555657143</v>
       </c>
       <c r="Q94">
-        <v>204.5979093942856</v>
+        <v>197.5016444342856</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3537186694964632</v>
+        <v>0.3977070508531009</v>
       </c>
       <c r="T94">
-        <v>6.001907997204211</v>
+        <v>6.859323425376243</v>
       </c>
       <c r="U94">
         <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.1650452703705273</v>
+        <v>0.1632705900439625</v>
       </c>
       <c r="W94">
-        <v>0.09902563093405548</v>
+        <v>0.09923610802078606</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8252263518526366</v>
+        <v>0.8163529502198126</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1201290740190481</v>
+        <v>0.1208570740190481</v>
       </c>
       <c r="C95">
-        <v>-3848.389819579275</v>
+        <v>-3947.869083285773</v>
       </c>
       <c r="D95">
-        <v>2545.266180420725</v>
+        <v>2520.578916714227</v>
       </c>
       <c r="E95">
-        <v>4618.856</v>
+        <v>4693.648</v>
       </c>
       <c r="F95">
-        <v>6955.656</v>
+        <v>7030.448</v>
       </c>
       <c r="G95">
         <v>562</v>
@@ -9077,37 +9077,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M95">
-        <v>824.9408016000001</v>
+        <v>833.8111328000001</v>
       </c>
       <c r="N95">
-        <v>-151.4979444571429</v>
+        <v>-160.3682756571429</v>
       </c>
       <c r="O95">
-        <v>-30.29958889142858</v>
+        <v>-32.07365513142859</v>
       </c>
       <c r="P95">
-        <v>-121.1983555657143</v>
+        <v>-128.2946205257144</v>
       </c>
       <c r="Q95">
-        <v>197.5016444342856</v>
+        <v>190.4053794742856</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3977070508531009</v>
+        <v>0.4563582259952845</v>
       </c>
       <c r="T95">
-        <v>6.859323425376243</v>
+        <v>8.002543996272285</v>
       </c>
       <c r="U95">
         <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.1632705900439625</v>
+        <v>0.1615336688732821</v>
       </c>
       <c r="W95">
-        <v>0.09923610802078606</v>
+        <v>0.09944210687162876</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8163529502198126</v>
+        <v>0.8076683443664103</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1208570740190481</v>
+        <v>0.2014803686300201</v>
       </c>
       <c r="C96">
-        <v>-3947.869083285773</v>
+        <v>-5328.01113082715</v>
       </c>
       <c r="D96">
-        <v>2520.578916714227</v>
+        <v>1215.228869172851</v>
       </c>
       <c r="E96">
-        <v>4693.648</v>
+        <v>4768.440000000001</v>
       </c>
       <c r="F96">
-        <v>7030.448</v>
+        <v>7105.240000000001</v>
       </c>
       <c r="G96">
         <v>562</v>
@@ -9159,45 +9159,45 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M96">
-        <v>833.8111328000001</v>
+        <v>1426.732192</v>
       </c>
       <c r="N96">
-        <v>-160.3682756571429</v>
+        <v>-753.289334857143</v>
       </c>
       <c r="O96">
-        <v>-32.07365513142859</v>
+        <v>-150.6578669714286</v>
       </c>
       <c r="P96">
-        <v>-128.2946205257144</v>
+        <v>-602.6314678857144</v>
       </c>
       <c r="Q96">
-        <v>190.4053794742856</v>
+        <v>-283.9314678857145</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4563582259952845</v>
+        <v>0.5745757634137811</v>
       </c>
       <c r="T96">
-        <v>8.002543996272285</v>
+        <v>10.30682383874547</v>
       </c>
       <c r="U96">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1615336688732821</v>
+        <v>0.09440354131195733</v>
       </c>
       <c r="W96">
-        <v>0.09944210687162876</v>
+        <v>0.181843768904559</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8076683443664103</v>
+        <v>0.4720177065597866</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2014803686300201</v>
+        <v>0.20303036863002</v>
       </c>
       <c r="C97">
-        <v>-5328.01113082715</v>
+        <v>-5414.783034987078</v>
       </c>
       <c r="D97">
-        <v>1215.228869172851</v>
+        <v>1203.248965012922</v>
       </c>
       <c r="E97">
-        <v>4768.440000000001</v>
+        <v>4843.232</v>
       </c>
       <c r="F97">
-        <v>7105.240000000001</v>
+        <v>7180.032</v>
       </c>
       <c r="G97">
         <v>562</v>
@@ -9241,37 +9241,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M97">
-        <v>1426.732192</v>
+        <v>1441.7504256</v>
       </c>
       <c r="N97">
-        <v>-753.289334857143</v>
+        <v>-768.3075684571428</v>
       </c>
       <c r="O97">
-        <v>-150.6578669714286</v>
+        <v>-153.6615136914286</v>
       </c>
       <c r="P97">
-        <v>-602.6314678857144</v>
+        <v>-614.6460547657142</v>
       </c>
       <c r="Q97">
-        <v>-283.9314678857145</v>
+        <v>-295.9460547657143</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5745757634137811</v>
+        <v>0.7067697042672267</v>
       </c>
       <c r="T97">
-        <v>10.30682383874547</v>
+        <v>12.88352979843184</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09440354131195733</v>
+        <v>0.09342017108995777</v>
       </c>
       <c r="W97">
-        <v>0.181843768904559</v>
+        <v>0.1820412296451365</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4720177065597866</v>
+        <v>0.4671008554497889</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2030303686300201</v>
+        <v>0.20458036863002</v>
       </c>
       <c r="C98">
-        <v>-5414.783034987078</v>
+        <v>-5501.321045604523</v>
       </c>
       <c r="D98">
-        <v>1203.248965012921</v>
+        <v>1191.502954395477</v>
       </c>
       <c r="E98">
-        <v>4843.231999999999</v>
+        <v>4918.023999999999</v>
       </c>
       <c r="F98">
-        <v>7180.031999999999</v>
+        <v>7254.824</v>
       </c>
       <c r="G98">
         <v>562</v>
@@ -9323,37 +9323,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M98">
-        <v>1441.7504256</v>
+        <v>1456.7686592</v>
       </c>
       <c r="N98">
-        <v>-768.3075684571428</v>
+        <v>-783.3258020571428</v>
       </c>
       <c r="O98">
-        <v>-153.6615136914286</v>
+        <v>-156.6651604114286</v>
       </c>
       <c r="P98">
-        <v>-614.6460547657142</v>
+        <v>-626.6606416457142</v>
       </c>
       <c r="Q98">
-        <v>-295.9460547657143</v>
+        <v>-307.9606416457143</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.706769704267225</v>
+        <v>0.9270929390229667</v>
       </c>
       <c r="T98">
-        <v>12.88352979843181</v>
+        <v>17.17803973124241</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09342017108995777</v>
+        <v>0.09245707654263863</v>
       </c>
       <c r="W98">
-        <v>0.1820412296451365</v>
+        <v>0.1822346190302382</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4671008554497889</v>
+        <v>0.4622853827131931</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.20458036863002</v>
+        <v>0.20613036863002</v>
       </c>
       <c r="C99">
-        <v>-5501.321045604523</v>
+        <v>-5587.631946203915</v>
       </c>
       <c r="D99">
-        <v>1191.502954395477</v>
+        <v>1179.984053796085</v>
       </c>
       <c r="E99">
-        <v>4918.023999999999</v>
+        <v>4992.816</v>
       </c>
       <c r="F99">
-        <v>7254.824</v>
+        <v>7329.616</v>
       </c>
       <c r="G99">
         <v>562</v>
@@ -9405,37 +9405,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M99">
-        <v>1456.7686592</v>
+        <v>1471.7868928</v>
       </c>
       <c r="N99">
-        <v>-783.3258020571428</v>
+        <v>-798.3440356571429</v>
       </c>
       <c r="O99">
-        <v>-156.6651604114286</v>
+        <v>-159.6688071314286</v>
       </c>
       <c r="P99">
-        <v>-626.6606416457142</v>
+        <v>-638.6752285257143</v>
       </c>
       <c r="Q99">
-        <v>-307.9606416457143</v>
+        <v>-319.9752285257143</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9270929390229667</v>
+        <v>1.36773940853445</v>
       </c>
       <c r="T99">
-        <v>17.17803973124241</v>
+        <v>25.76705959686362</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09245707654263863</v>
+        <v>0.09151363698608109</v>
       </c>
       <c r="W99">
-        <v>0.1822346190302382</v>
+        <v>0.1824240616931949</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4622853827131931</v>
+        <v>0.4575681849304054</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.20613036863002</v>
+        <v>0.20768036863002</v>
       </c>
       <c r="C100">
-        <v>-5587.631946203915</v>
+        <v>-5673.722260501456</v>
       </c>
       <c r="D100">
-        <v>1179.984053796085</v>
+        <v>1168.685739498544</v>
       </c>
       <c r="E100">
-        <v>4992.816</v>
+        <v>5067.607999999999</v>
       </c>
       <c r="F100">
-        <v>7329.616</v>
+        <v>7404.407999999999</v>
       </c>
       <c r="G100">
         <v>562</v>
@@ -9487,37 +9487,37 @@
         <v>673.4428571428572</v>
       </c>
       <c r="M100">
-        <v>1471.7868928</v>
+        <v>1486.8051264</v>
       </c>
       <c r="N100">
-        <v>-798.3440356571429</v>
+        <v>-813.3622692571427</v>
       </c>
       <c r="O100">
-        <v>-159.6688071314286</v>
+        <v>-162.6724538514285</v>
       </c>
       <c r="P100">
-        <v>-638.6752285257143</v>
+        <v>-650.6898154057142</v>
       </c>
       <c r="Q100">
-        <v>-319.9752285257143</v>
+        <v>-331.9898154057142</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.36773940853445</v>
+        <v>2.6896788170689</v>
       </c>
       <c r="T100">
-        <v>25.76705959686362</v>
+        <v>51.53411919372724</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09151363698608109</v>
+        <v>0.09058925681450453</v>
       </c>
       <c r="W100">
-        <v>0.1824240616931949</v>
+        <v>0.1826096772316475</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4575681849304054</v>
+        <v>0.4529462840725226</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.20768036863002</v>
-      </c>
-      <c r="C101">
-        <v>-5673.722260501456</v>
-      </c>
-      <c r="D101">
-        <v>1168.685739498544</v>
-      </c>
-      <c r="E101">
-        <v>5067.607999999999</v>
-      </c>
-      <c r="F101">
-        <v>7404.407999999999</v>
-      </c>
-      <c r="G101">
-        <v>562</v>
-      </c>
-      <c r="H101">
-        <v>5142.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>992.1428571428571</v>
-      </c>
-      <c r="K101">
-        <v>318.6999999999999</v>
-      </c>
-      <c r="L101">
-        <v>673.4428571428572</v>
-      </c>
-      <c r="M101">
-        <v>1486.8051264</v>
-      </c>
-      <c r="N101">
-        <v>-813.3622692571427</v>
-      </c>
-      <c r="O101">
-        <v>-162.6724538514285</v>
-      </c>
-      <c r="P101">
-        <v>-650.6898154057142</v>
-      </c>
-      <c r="Q101">
-        <v>-331.9898154057142</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.6896788170689</v>
-      </c>
-      <c r="T101">
-        <v>51.53411919372724</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09058925681450453</v>
-      </c>
-      <c r="W101">
-        <v>0.1826096772316475</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4529462840725226</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
